--- a/storage/app/wage-template/ledger-format.xlsx
+++ b/storage/app/wage-template/ledger-format.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\devbox\karte\dev_docker\app\karte\storage\app\wage-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0355256E-7BA8-4B86-B243-BB322B84A3C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF77731B-9987-4E4E-9C58-6C67C3927BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26910" yWindow="795" windowWidth="25440" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$V$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$V$35</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>賃金計算期間</t>
     <rPh sb="0" eb="2">
@@ -47,49 +47,6 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>キカン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>労働日数</t>
-    <rPh sb="0" eb="2">
-      <t>ロウドウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニッスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>労働時間数</t>
-    <rPh sb="0" eb="2">
-      <t>ロウドウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ジカンスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>休日労働時間数</t>
-    <rPh sb="0" eb="2">
-      <t>キュウジツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ロウドウ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>ジカンスウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>残業時間数</t>
-    <rPh sb="0" eb="2">
-      <t>ザンギョウ</t>
-    </rPh>
-    <rPh sb="2" eb="5">
-      <t>ジカンスウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -146,19 +103,6 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>トバリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>控除合計額</t>
-    <rPh sb="0" eb="2">
-      <t>コウジョ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ゴウケイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ガク</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -283,16 +227,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>支給合計</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>非課税支給額</t>
-  </si>
-  <si>
-    <t>課税対象額</t>
-  </si>
-  <si>
     <t>対象期間</t>
     <rPh sb="0" eb="4">
       <t>タイショウキカン</t>
@@ -316,37 +250,44 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>有給取得日数</t>
-    <rPh sb="0" eb="2">
-      <t>ユウキュウ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ニッスウ</t>
+    <t>【備考】</t>
+    <rPh sb="1" eb="3">
+      <t>ビコウ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>欠勤日数</t>
-    <rPh sb="0" eb="2">
-      <t>ケッキン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ニッスウ</t>
-    </rPh>
+    <t>非課税支給額</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>【備考】</t>
-    <rPh sb="1" eb="3">
-      <t>ビコウ</t>
-    </rPh>
+    <t>課税支給額</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>深夜労働時間数</t>
+    <t xml:space="preserve">労働保険対象賃金	</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t xml:space="preserve">社会保険対象賃金	</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>控除合計額</t>
+    <rPh sb="0" eb="2">
+      <t>コウジョ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ゴウケイガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支給合計額</t>
+    <rPh sb="2" eb="5">
+      <t>ゴウケイガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -356,7 +297,7 @@
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;月&quot;&quot;分&quot;"/>
-    <numFmt numFmtId="185" formatCode="#,##0_);[Red]\(#,##0\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -1219,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1253,9 +1194,6 @@
     <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1277,176 +1215,245 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="43" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="49" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="51" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="60" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="43" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="49" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="51" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="60" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
@@ -1466,15 +1473,6 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1483,72 +1481,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="185" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1930,7 +1862,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AP31"/>
+  <dimension ref="B2:AP35"/>
   <sheetFormatPr defaultRowHeight="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="3.625" customWidth="1"/>
@@ -1939,29 +1871,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="88" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="89"/>
-      <c r="N2" s="89"/>
-      <c r="O2" s="89"/>
-      <c r="P2" s="89"/>
-      <c r="Q2" s="89"/>
-      <c r="R2" s="89"/>
-      <c r="S2" s="89"/>
-      <c r="T2" s="89"/>
-      <c r="U2" s="89"/>
-      <c r="V2" s="90"/>
+      <c r="B2" s="82" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="84"/>
     </row>
     <row r="3" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="7"/>
@@ -1986,152 +1918,152 @@
       <c r="U3" s="7"/>
     </row>
     <row r="4" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="84"/>
-      <c r="F4" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="75"/>
-      <c r="K4" s="84"/>
-      <c r="L4" s="74" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="75"/>
-      <c r="N4" s="84"/>
+      <c r="B4" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="80"/>
+      <c r="D4" s="81"/>
+      <c r="F4" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="J4" s="80"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="80"/>
+      <c r="N4" s="81"/>
       <c r="O4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P4" s="74" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q4" s="84"/>
+        <v>18</v>
+      </c>
+      <c r="P4" s="79" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q4" s="81"/>
       <c r="R4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4" s="79" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="81"/>
+      <c r="U4" s="79" t="s">
         <v>8</v>
       </c>
-      <c r="S4" s="74" t="s">
-        <v>24</v>
-      </c>
-      <c r="T4" s="84"/>
-      <c r="U4" s="74" t="s">
-        <v>13</v>
-      </c>
-      <c r="V4" s="84"/>
+      <c r="V4" s="81"/>
     </row>
     <row r="5" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="74"/>
-      <c r="C5" s="75"/>
-      <c r="D5" s="84"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="75"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="75"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="84"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="81"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="79"/>
+      <c r="M5" s="80"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="81"/>
       <c r="R5" s="5"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="81"/>
-      <c r="U5" s="80"/>
-      <c r="V5" s="81"/>
+      <c r="S5" s="102"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="102"/>
+      <c r="V5" s="103"/>
     </row>
     <row r="6" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="98"/>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="97" t="s">
+      <c r="B7" s="91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
+      <c r="L7" s="92"/>
+      <c r="M7" s="92"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="91" t="s">
+        <v>12</v>
+      </c>
+      <c r="R7" s="92"/>
+      <c r="S7" s="92"/>
+      <c r="T7" s="92"/>
+      <c r="U7" s="93"/>
+      <c r="V7" s="88" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="94" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="8" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="83" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="82"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="102" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="14"/>
-      <c r="U8" s="100" t="s">
-        <v>19</v>
-      </c>
-      <c r="V8" s="95"/>
+      <c r="B8" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="78"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="96" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="13"/>
+      <c r="U8" s="94" t="s">
+        <v>14</v>
+      </c>
+      <c r="V8" s="89"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="93"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="20"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="102"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="101"/>
-      <c r="V9" s="96"/>
+      <c r="B9" s="86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="87"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="96"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="95"/>
+      <c r="V9" s="90"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="6"/>
@@ -2150,790 +2082,848 @@
       <c r="AL9" s="6"/>
       <c r="AM9" s="6"/>
       <c r="AN9" s="6"/>
-      <c r="AO9" s="18"/>
-      <c r="AP9" s="18"/>
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
     </row>
     <row r="10" spans="2:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="91"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="103">
+      <c r="B10" s="85"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="30"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="70">
         <f t="shared" ref="V10" si="0">P10+U10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="91"/>
-      <c r="C11" s="63"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="36"/>
-      <c r="V11" s="103">
+      <c r="B11" s="85"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="70">
         <f>P11+U11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="91"/>
-      <c r="C12" s="22" t="s">
+      <c r="B12" s="85"/>
+      <c r="C12" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="42"/>
+      <c r="V12" s="71">
+        <f t="shared" ref="V12:V17" si="1">P12+U12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="85"/>
+      <c r="C13" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="39"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="40"/>
+      <c r="V13" s="72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="85"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="42"/>
+      <c r="V14" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="85"/>
+      <c r="C15" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="22"/>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="22"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="71">
+        <f t="shared" ref="V15:V16" si="2">P15+U15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="85"/>
+      <c r="C16" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="23"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="25"/>
-      <c r="U12" s="44"/>
-      <c r="V12" s="104">
-        <f t="shared" ref="V12" si="1">P12+U12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="91"/>
-      <c r="C13" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="40"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="40"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="42"/>
-      <c r="V13" s="105">
-        <f t="shared" ref="V13:V21" si="2">P13+U13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="64"/>
-      <c r="C14" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="3">
-        <f t="shared" ref="D14:O14" si="3">SUM(D10:D11)</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
+      <c r="G16" s="38"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
+      <c r="K16" s="38"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="39"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="39"/>
+      <c r="U16" s="40"/>
+      <c r="V16" s="72">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="85"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+      <c r="J17" s="38"/>
+      <c r="K17" s="38"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="39"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="38"/>
+      <c r="S17" s="38"/>
+      <c r="T17" s="38"/>
+      <c r="U17" s="40"/>
+      <c r="V17" s="70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="60"/>
+      <c r="C18" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="3">
+        <f>SUM(D10:D11)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" ref="D18:O18" si="3">SUM(E10:E11)</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O18" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O14" s="3">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="16">
-        <f>SUM(D14:O14)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14" s="10">
-        <f>SUM(Q10:Q11)</f>
-        <v>0</v>
-      </c>
-      <c r="R14" s="10">
-        <f t="shared" ref="R14:T14" si="4">SUM(R10:R11)</f>
-        <v>0</v>
-      </c>
-      <c r="S14" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="T14" s="10">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="U14" s="16">
-        <f>SUM(Q14:T14)</f>
-        <v>0</v>
-      </c>
-      <c r="V14" s="106">
-        <f>P14+U14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="31"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="31"/>
-      <c r="N15" s="31"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="30"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="107">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="79"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="33"/>
-      <c r="V16" s="107">
-        <f t="shared" ref="V16" si="5">P16+U16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="79"/>
-      <c r="C17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="3">
-        <f>SUM(D15:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="3">
-        <f t="shared" ref="E17:O17" si="6">SUM(E15:E16)</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="3">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="16">
-        <f>SUM(D17:O17)</f>
-        <v>0</v>
-      </c>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="3"/>
-      <c r="S17" s="3"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="106">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="79"/>
-      <c r="C18" s="65"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="66"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
-      <c r="H18" s="66"/>
-      <c r="I18" s="66"/>
-      <c r="J18" s="66"/>
-      <c r="K18" s="66"/>
-      <c r="L18" s="66"/>
-      <c r="M18" s="66"/>
-      <c r="N18" s="66"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="69"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="66"/>
-      <c r="T18" s="67"/>
-      <c r="U18" s="68"/>
-      <c r="V18" s="108">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="79"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="31"/>
-      <c r="N19" s="31"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="30"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="31"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="33"/>
-      <c r="V19" s="107">
-        <f t="shared" si="2"/>
+      <c r="P18" s="15">
+        <f>SUM(D18:O18)</f>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="15">
+        <f>SUM(R18:T18)</f>
+        <v>0</v>
+      </c>
+      <c r="V18" s="73">
+        <f>P18+U18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="24"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="29"/>
+      <c r="O19" s="30"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="28"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="74">
+        <f t="shared" ref="V17:V25" si="4">P19+U19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="82" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="82"/>
-      <c r="D20" s="4">
-        <f t="shared" ref="D20:O20" si="7">SUM(D17:D19)</f>
-        <v>0</v>
-      </c>
-      <c r="E20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="4">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="16">
-        <f>SUM(D20:O20)</f>
-        <v>0</v>
-      </c>
-      <c r="Q20" s="10">
-        <f>SUM(Q17:Q19)</f>
-        <v>0</v>
-      </c>
-      <c r="R20" s="10">
-        <f t="shared" ref="R20:S20" si="8">SUM(R17:R19)</f>
-        <v>0</v>
-      </c>
-      <c r="S20" s="10">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T20" s="10">
-        <f>SUM(T17:T19)</f>
-        <v>0</v>
-      </c>
-      <c r="U20" s="16">
-        <f>SUM(Q20:T20)</f>
-        <v>0</v>
-      </c>
-      <c r="V20" s="106">
+      <c r="B20" s="101"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="74">
         <f>P20+U20</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="83" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="82"/>
+      <c r="B21" s="101"/>
+      <c r="C21" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="15"/>
-      <c r="P21" s="16"/>
+        <f>SUM(D19:D20)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <f t="shared" ref="E21:O21" si="5">SUM(E19:E20)</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O21" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="15">
+        <f>SUM(D21:O21)</f>
+        <v>0</v>
+      </c>
       <c r="Q21" s="10"/>
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
-      <c r="T21" s="15"/>
-      <c r="U21" s="16"/>
-      <c r="V21" s="106">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="76" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="8">
-        <f t="shared" ref="D22:O22" si="9">SUM(D14-D20)</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="F22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="G22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="8">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="17">
-        <f>SUM(D22:O22)</f>
-        <v>0</v>
-      </c>
-      <c r="Q22" s="11">
-        <f>(Q14-Q20)</f>
-        <v>0</v>
-      </c>
-      <c r="R22" s="11">
-        <f t="shared" ref="R22:T22" si="10">(R14-R20)</f>
-        <v>0</v>
-      </c>
-      <c r="S22" s="11">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="T22" s="11">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="U22" s="17">
-        <f>SUM(Q22:T22)</f>
-        <v>0</v>
-      </c>
-      <c r="V22" s="109">
-        <f>P22+U22</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="101"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="63"/>
+      <c r="U22" s="64"/>
+      <c r="V22" s="75">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="101"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="74">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
     <row r="24" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="D24" s="51">
-        <v>0</v>
-      </c>
-      <c r="E24" s="51"/>
-      <c r="F24" s="51"/>
-      <c r="G24" s="51"/>
-      <c r="H24" s="51"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="51"/>
-      <c r="K24" s="51"/>
-      <c r="L24" s="51"/>
-      <c r="M24" s="51"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="52"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="73" t="s">
-        <v>32</v>
-      </c>
-      <c r="R24" s="54"/>
-      <c r="S24" s="54"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="55"/>
-      <c r="V24" s="9"/>
+      <c r="B24" s="77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="78"/>
+      <c r="D24" s="4">
+        <f t="shared" ref="D24:O24" si="6">SUM(D21:D23)</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="15">
+        <f>SUM(D24:O24)</f>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="15">
+        <f>SUM(Q24:T24)</f>
+        <v>0</v>
+      </c>
+      <c r="V24" s="73">
+        <f>P24+U24</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="86"/>
-      <c r="C25" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="70">
-        <v>0</v>
-      </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="71"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="46"/>
-      <c r="R25" s="47"/>
-      <c r="S25" s="47"/>
-      <c r="T25" s="47"/>
-      <c r="U25" s="48"/>
-      <c r="V25" s="49"/>
-    </row>
-    <row r="26" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="86"/>
-      <c r="C26" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="70">
-        <v>0</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="46"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="47"/>
-      <c r="T26" s="47"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="49"/>
-    </row>
-    <row r="27" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="86"/>
-      <c r="C27" s="26" t="s">
+      <c r="B25" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="D27" s="27">
-        <v>0</v>
-      </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="49"/>
-    </row>
+      <c r="C25" s="78"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="15"/>
+      <c r="V25" s="73">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="98" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="99"/>
+      <c r="D26" s="8">
+        <f t="shared" ref="D26:O26" si="7">SUM(D18-D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="16">
+        <f>SUM(D26:O26)</f>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="16">
+        <f>SUM(Q26:T26)</f>
+        <v>0</v>
+      </c>
+      <c r="V26" s="76">
+        <f>P26+U26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="28" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="86"/>
-      <c r="C28" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="31">
-        <v>0</v>
-      </c>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="33"/>
-      <c r="Q28" s="46"/>
-      <c r="R28" s="47"/>
-      <c r="S28" s="47"/>
-      <c r="T28" s="47"/>
-      <c r="U28" s="47"/>
-      <c r="V28" s="49"/>
+      <c r="B28" s="104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="46"/>
+      <c r="D28" s="47"/>
+      <c r="E28" s="47"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="47"/>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="47"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
+      <c r="N28" s="47"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="51"/>
+      <c r="V28" s="9"/>
     </row>
     <row r="29" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="86"/>
-      <c r="C29" s="26" t="s">
-        <v>4</v>
-      </c>
-      <c r="D29" s="31">
-        <v>0</v>
-      </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="33"/>
-      <c r="Q29" s="46"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="47"/>
-      <c r="T29" s="47"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="49"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
+      <c r="H29" s="66"/>
+      <c r="I29" s="66"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="97"/>
+      <c r="S29" s="97"/>
+      <c r="T29" s="97"/>
+      <c r="U29" s="97"/>
+      <c r="V29" s="45"/>
     </row>
     <row r="30" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="86"/>
-      <c r="C30" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="34">
-        <v>0</v>
-      </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="47"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="49"/>
-    </row>
-    <row r="31" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="87"/>
-      <c r="C31" s="56"/>
-      <c r="D31" s="57"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="57"/>
-      <c r="H31" s="57"/>
-      <c r="I31" s="57"/>
-      <c r="J31" s="57"/>
-      <c r="K31" s="57"/>
-      <c r="L31" s="57"/>
-      <c r="M31" s="57"/>
-      <c r="N31" s="57"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="59"/>
-      <c r="Q31" s="60"/>
-      <c r="R31" s="61"/>
-      <c r="S31" s="61"/>
-      <c r="T31" s="61"/>
-      <c r="U31" s="61"/>
-      <c r="V31" s="62"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="66"/>
+      <c r="G30" s="66"/>
+      <c r="H30" s="66"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="67"/>
+      <c r="P30" s="68"/>
+      <c r="Q30" s="44"/>
+      <c r="R30" s="97"/>
+      <c r="S30" s="97"/>
+      <c r="T30" s="97"/>
+      <c r="U30" s="97"/>
+      <c r="V30" s="45"/>
+    </row>
+    <row r="31" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="105"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="44"/>
+      <c r="R31" s="97"/>
+      <c r="S31" s="97"/>
+      <c r="T31" s="97"/>
+      <c r="U31" s="97"/>
+      <c r="V31" s="45"/>
+    </row>
+    <row r="32" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="105"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="44"/>
+      <c r="R32" s="97"/>
+      <c r="S32" s="97"/>
+      <c r="T32" s="97"/>
+      <c r="U32" s="97"/>
+      <c r="V32" s="45"/>
+    </row>
+    <row r="33" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="105"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="29"/>
+      <c r="N33" s="29"/>
+      <c r="O33" s="30"/>
+      <c r="P33" s="31"/>
+      <c r="Q33" s="44"/>
+      <c r="R33" s="97"/>
+      <c r="S33" s="97"/>
+      <c r="T33" s="97"/>
+      <c r="U33" s="97"/>
+      <c r="V33" s="45"/>
+    </row>
+    <row r="34" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="105"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
+      <c r="F34" s="32"/>
+      <c r="G34" s="32"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="44"/>
+      <c r="R34" s="97"/>
+      <c r="S34" s="97"/>
+      <c r="T34" s="97"/>
+      <c r="U34" s="97"/>
+      <c r="V34" s="45"/>
+    </row>
+    <row r="35" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="106"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="53"/>
+      <c r="I35" s="53"/>
+      <c r="J35" s="53"/>
+      <c r="K35" s="53"/>
+      <c r="L35" s="53"/>
+      <c r="M35" s="53"/>
+      <c r="N35" s="53"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="55"/>
+      <c r="Q35" s="56"/>
+      <c r="R35" s="57"/>
+      <c r="S35" s="57"/>
+      <c r="T35" s="57"/>
+      <c r="U35" s="57"/>
+      <c r="V35" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
+    <mergeCell ref="R29:U34"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="S4:T4"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="U5:V5"/>
-    <mergeCell ref="B24:B31"/>
+    <mergeCell ref="B28:B35"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="I5:K5"/>
     <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B10:B17"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B9:C9"/>
@@ -2942,21 +2932,6 @@
     <mergeCell ref="Q7:U7"/>
     <mergeCell ref="U8:U9"/>
     <mergeCell ref="P8:P9"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S4:T4"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.27559055118110237" right="0.11811023622047245" top="0.27559055118110237" bottom="0.19685039370078741" header="0" footer="0"/>

--- a/storage/app/wage-template/ledger-format.xlsx
+++ b/storage/app/wage-template/ledger-format.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\devbox\karte\dev_docker\app\karte\storage\app\wage-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF77731B-9987-4E4E-9C58-6C67C3927BC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55793591-7109-4840-B9BD-D0A7FFB2ED66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$V$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$V$34</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>賃金計算期間</t>
     <rPh sb="0" eb="2">
@@ -57,16 +57,6 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>ガク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>実物給与</t>
-    <rPh sb="0" eb="2">
-      <t>ジツブツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キュウヨ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -1392,21 +1382,51 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1451,36 +1471,6 @@
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1862,7 +1852,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AP35"/>
+  <dimension ref="B2:AP34"/>
   <sheetFormatPr defaultRowHeight="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="3.625" customWidth="1"/>
@@ -1871,29 +1861,29 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="82" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="84"/>
+      <c r="B2" s="92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
+      <c r="Q2" s="93"/>
+      <c r="R2" s="93"/>
+      <c r="S2" s="93"/>
+      <c r="T2" s="93"/>
+      <c r="U2" s="93"/>
+      <c r="V2" s="94"/>
     </row>
     <row r="3" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="7"/>
@@ -1918,102 +1908,102 @@
       <c r="U3" s="7"/>
     </row>
     <row r="4" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="79" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="80"/>
-      <c r="D4" s="81"/>
-      <c r="F4" s="79" t="s">
+      <c r="B4" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="79"/>
+      <c r="D4" s="88"/>
+      <c r="F4" s="78" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="79"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="80"/>
-      <c r="H4" s="80"/>
-      <c r="I4" s="79" t="s">
+      <c r="J4" s="79"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="79"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="78" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="T4" s="88"/>
+      <c r="U4" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="80"/>
-      <c r="K4" s="81"/>
-      <c r="L4" s="79" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="80"/>
-      <c r="N4" s="81"/>
-      <c r="O4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="P4" s="79" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="81"/>
-      <c r="R4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="S4" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="T4" s="81"/>
-      <c r="U4" s="79" t="s">
-        <v>8</v>
-      </c>
-      <c r="V4" s="81"/>
+      <c r="V4" s="88"/>
     </row>
     <row r="5" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="79"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="81"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="81"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="88"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="78"/>
+      <c r="M5" s="79"/>
+      <c r="N5" s="88"/>
       <c r="O5" s="43"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="81"/>
+      <c r="P5" s="78"/>
+      <c r="Q5" s="88"/>
       <c r="R5" s="5"/>
-      <c r="S5" s="102"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="102"/>
-      <c r="V5" s="103"/>
+      <c r="S5" s="84"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="84"/>
+      <c r="V5" s="85"/>
     </row>
     <row r="6" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="101" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="102"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="102"/>
+      <c r="L7" s="102"/>
+      <c r="M7" s="102"/>
+      <c r="N7" s="102"/>
+      <c r="O7" s="102"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="93"/>
-      <c r="Q7" s="91" t="s">
-        <v>12</v>
-      </c>
-      <c r="R7" s="92"/>
-      <c r="S7" s="92"/>
-      <c r="T7" s="92"/>
-      <c r="U7" s="93"/>
-      <c r="V7" s="88" t="s">
-        <v>17</v>
+      <c r="R7" s="102"/>
+      <c r="S7" s="102"/>
+      <c r="T7" s="102"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="98" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="77" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="78"/>
+      <c r="B8" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="87"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
@@ -2026,25 +2016,25 @@
       <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="13"/>
-      <c r="P8" s="96" t="s">
-        <v>13</v>
+      <c r="P8" s="106" t="s">
+        <v>12</v>
       </c>
       <c r="Q8" s="12"/>
       <c r="R8" s="11"/>
       <c r="S8" s="11"/>
       <c r="T8" s="13"/>
-      <c r="U8" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="V8" s="89"/>
+      <c r="U8" s="104" t="s">
+        <v>13</v>
+      </c>
+      <c r="V8" s="99"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="86" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="87"/>
+      <c r="B9" s="96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="97"/>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
       <c r="F9" s="18"/>
@@ -2057,13 +2047,13 @@
       <c r="M9" s="18"/>
       <c r="N9" s="18"/>
       <c r="O9" s="19"/>
-      <c r="P9" s="96"/>
+      <c r="P9" s="106"/>
       <c r="Q9" s="36"/>
       <c r="R9" s="18"/>
       <c r="S9" s="18"/>
       <c r="T9" s="19"/>
-      <c r="U9" s="95"/>
-      <c r="V9" s="90"/>
+      <c r="U9" s="105"/>
+      <c r="V9" s="100"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="6"/>
@@ -2086,7 +2076,7 @@
       <c r="AP9" s="17"/>
     </row>
     <row r="10" spans="2:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="85"/>
+      <c r="B10" s="95"/>
       <c r="C10" s="24"/>
       <c r="D10" s="29"/>
       <c r="E10" s="29"/>
@@ -2112,7 +2102,7 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="85"/>
+      <c r="B11" s="95"/>
       <c r="C11" s="59"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
@@ -2138,9 +2128,9 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="85"/>
+      <c r="B12" s="95"/>
       <c r="C12" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="22"/>
       <c r="E12" s="22"/>
@@ -2166,9 +2156,9 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="85"/>
+      <c r="B13" s="95"/>
       <c r="C13" s="37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13" s="38"/>
       <c r="E13" s="38"/>
@@ -2194,7 +2184,7 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="85"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="20"/>
       <c r="D14" s="22"/>
       <c r="E14" s="22"/>
@@ -2220,9 +2210,9 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="85"/>
+      <c r="B15" s="95"/>
       <c r="C15" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22"/>
@@ -2248,9 +2238,9 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="85"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="37" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="38"/>
       <c r="E16" s="38"/>
@@ -2276,7 +2266,7 @@
       </c>
     </row>
     <row r="17" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="85"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="37"/>
       <c r="D17" s="38"/>
       <c r="E17" s="38"/>
@@ -2304,14 +2294,14 @@
     <row r="18" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="60"/>
       <c r="C18" s="37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="3">
         <f>SUM(D10:D11)</f>
         <v>0</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" ref="D18:O18" si="3">SUM(E10:E11)</f>
+        <f t="shared" ref="E18:O18" si="3">SUM(E10:E11)</f>
         <v>0</v>
       </c>
       <c r="F18" s="3">
@@ -2372,7 +2362,7 @@
       </c>
     </row>
     <row r="19" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="100" t="s">
+      <c r="B19" s="82" t="s">
         <v>1</v>
       </c>
       <c r="C19" s="24"/>
@@ -2395,12 +2385,12 @@
       <c r="T19" s="30"/>
       <c r="U19" s="31"/>
       <c r="V19" s="74">
-        <f t="shared" ref="V17:V25" si="4">P19+U19</f>
+        <f t="shared" ref="V19:V23" si="4">P19+U19</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="101"/>
+      <c r="B20" s="83"/>
       <c r="C20" s="24"/>
       <c r="D20" s="29"/>
       <c r="E20" s="29"/>
@@ -2426,9 +2416,9 @@
       </c>
     </row>
     <row r="21" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="101"/>
+      <c r="B21" s="83"/>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(D19:D20)</f>
@@ -2493,7 +2483,7 @@
       </c>
     </row>
     <row r="22" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="101"/>
+      <c r="B22" s="83"/>
       <c r="C22" s="61"/>
       <c r="D22" s="62"/>
       <c r="E22" s="62"/>
@@ -2519,7 +2509,7 @@
       </c>
     </row>
     <row r="23" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="101"/>
+      <c r="B23" s="83"/>
       <c r="C23" s="24"/>
       <c r="D23" s="29"/>
       <c r="E23" s="29"/>
@@ -2545,10 +2535,10 @@
       </c>
     </row>
     <row r="24" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="78"/>
+      <c r="B24" s="86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="87"/>
       <c r="D24" s="4">
         <f t="shared" ref="D24:O24" si="6">SUM(D21:D23)</f>
         <v>0</v>
@@ -2614,134 +2604,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="77" t="s">
+    <row r="25" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="78"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="15"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="8">
+        <f>SUM(D18-D24)</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="8">
+        <f t="shared" ref="D25:O25" si="7">SUM(E18-E24)</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O25" s="8">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="16">
+        <f>SUM(D25:O25)</f>
+        <v>0</v>
+      </c>
       <c r="Q25" s="10"/>
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="14"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="98" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="99"/>
-      <c r="D26" s="8">
-        <f t="shared" ref="D26:O26" si="7">SUM(D18-D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="F26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="16">
-        <f>SUM(D26:O26)</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="3"/>
-      <c r="S26" s="3"/>
-      <c r="T26" s="14"/>
-      <c r="U26" s="16">
-        <f>SUM(Q26:T26)</f>
-        <v>0</v>
-      </c>
-      <c r="V26" s="76">
-        <f>P26+U26</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+      <c r="U25" s="16">
+        <f>SUM(Q25:T25)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="76">
+        <f>P25+U25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="89" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="51"/>
+      <c r="V27" s="9"/>
+    </row>
     <row r="28" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="46"/>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="69" t="s">
-        <v>22</v>
-      </c>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="9"/>
+      <c r="B28" s="90"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="66"/>
+      <c r="E28" s="66"/>
+      <c r="F28" s="66"/>
+      <c r="G28" s="66"/>
+      <c r="H28" s="66"/>
+      <c r="I28" s="66"/>
+      <c r="J28" s="66"/>
+      <c r="K28" s="66"/>
+      <c r="L28" s="66"/>
+      <c r="M28" s="66"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="68"/>
+      <c r="Q28" s="44"/>
+      <c r="R28" s="77"/>
+      <c r="S28" s="77"/>
+      <c r="T28" s="77"/>
+      <c r="U28" s="77"/>
+      <c r="V28" s="45"/>
     </row>
     <row r="29" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="105"/>
+      <c r="B29" s="90"/>
       <c r="C29" s="61"/>
       <c r="D29" s="66"/>
       <c r="E29" s="66"/>
@@ -2757,60 +2742,60 @@
       <c r="O29" s="67"/>
       <c r="P29" s="68"/>
       <c r="Q29" s="44"/>
-      <c r="R29" s="97"/>
-      <c r="S29" s="97"/>
-      <c r="T29" s="97"/>
-      <c r="U29" s="97"/>
+      <c r="R29" s="77"/>
+      <c r="S29" s="77"/>
+      <c r="T29" s="77"/>
+      <c r="U29" s="77"/>
       <c r="V29" s="45"/>
     </row>
     <row r="30" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="105"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="66"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-      <c r="M30" s="66"/>
-      <c r="N30" s="66"/>
-      <c r="O30" s="67"/>
-      <c r="P30" s="68"/>
+      <c r="B30" s="90"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="27"/>
       <c r="Q30" s="44"/>
-      <c r="R30" s="97"/>
-      <c r="S30" s="97"/>
-      <c r="T30" s="97"/>
-      <c r="U30" s="97"/>
+      <c r="R30" s="77"/>
+      <c r="S30" s="77"/>
+      <c r="T30" s="77"/>
+      <c r="U30" s="77"/>
       <c r="V30" s="45"/>
     </row>
     <row r="31" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="105"/>
+      <c r="B31" s="90"/>
       <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="26"/>
-      <c r="P31" s="27"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="31"/>
       <c r="Q31" s="44"/>
-      <c r="R31" s="97"/>
-      <c r="S31" s="97"/>
-      <c r="T31" s="97"/>
-      <c r="U31" s="97"/>
+      <c r="R31" s="77"/>
+      <c r="S31" s="77"/>
+      <c r="T31" s="77"/>
+      <c r="U31" s="77"/>
       <c r="V31" s="45"/>
     </row>
     <row r="32" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="105"/>
+      <c r="B32" s="90"/>
       <c r="C32" s="24"/>
       <c r="D32" s="29"/>
       <c r="E32" s="29"/>
@@ -2826,100 +2811,60 @@
       <c r="O32" s="30"/>
       <c r="P32" s="31"/>
       <c r="Q32" s="44"/>
-      <c r="R32" s="97"/>
-      <c r="S32" s="97"/>
-      <c r="T32" s="97"/>
-      <c r="U32" s="97"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="77"/>
+      <c r="U32" s="77"/>
       <c r="V32" s="45"/>
     </row>
     <row r="33" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="105"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="30"/>
-      <c r="P33" s="31"/>
+      <c r="B33" s="90"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="34"/>
       <c r="Q33" s="44"/>
-      <c r="R33" s="97"/>
-      <c r="S33" s="97"/>
-      <c r="T33" s="97"/>
-      <c r="U33" s="97"/>
+      <c r="R33" s="77"/>
+      <c r="S33" s="77"/>
+      <c r="T33" s="77"/>
+      <c r="U33" s="77"/>
       <c r="V33" s="45"/>
     </row>
-    <row r="34" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="105"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
-      <c r="F34" s="32"/>
-      <c r="G34" s="32"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="97"/>
-      <c r="S34" s="97"/>
-      <c r="T34" s="97"/>
-      <c r="U34" s="97"/>
-      <c r="V34" s="45"/>
-    </row>
-    <row r="35" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="106"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="53"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="53"/>
-      <c r="I35" s="53"/>
-      <c r="J35" s="53"/>
-      <c r="K35" s="53"/>
-      <c r="L35" s="53"/>
-      <c r="M35" s="53"/>
-      <c r="N35" s="53"/>
-      <c r="O35" s="54"/>
-      <c r="P35" s="55"/>
-      <c r="Q35" s="56"/>
-      <c r="R35" s="57"/>
-      <c r="S35" s="57"/>
-      <c r="T35" s="57"/>
-      <c r="U35" s="57"/>
-      <c r="V35" s="58"/>
+    <row r="34" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="91"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="53"/>
+      <c r="G34" s="53"/>
+      <c r="H34" s="53"/>
+      <c r="I34" s="53"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="53"/>
+      <c r="L34" s="53"/>
+      <c r="M34" s="53"/>
+      <c r="N34" s="53"/>
+      <c r="O34" s="54"/>
+      <c r="P34" s="55"/>
+      <c r="Q34" s="56"/>
+      <c r="R34" s="57"/>
+      <c r="S34" s="57"/>
+      <c r="T34" s="57"/>
+      <c r="U34" s="57"/>
+      <c r="V34" s="58"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="R29:U34"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="B28:B35"/>
-    <mergeCell ref="B25:C25"/>
+  <mergeCells count="28">
     <mergeCell ref="I4:K4"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="B2:V2"/>
@@ -2932,6 +2877,22 @@
     <mergeCell ref="Q7:U7"/>
     <mergeCell ref="U8:U9"/>
     <mergeCell ref="P8:P9"/>
+    <mergeCell ref="R28:U33"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="B27:B34"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.27559055118110237" right="0.11811023622047245" top="0.27559055118110237" bottom="0.19685039370078741" header="0" footer="0"/>

--- a/storage/app/wage-template/ledger-format.xlsx
+++ b/storage/app/wage-template/ledger-format.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\devbox\karte\dev_docker\app\karte\storage\app\wage-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55793591-7109-4840-B9BD-D0A7FFB2ED66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9251A38-492C-4579-9AA0-B161FDB61752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$V$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">base!$B$2:$X$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
   <si>
     <t>賃金計算期間</t>
     <rPh sb="0" eb="2">
@@ -51,6 +51,49 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>労働日数</t>
+    <rPh sb="0" eb="2">
+      <t>ロウドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>労働時間数</t>
+    <rPh sb="0" eb="2">
+      <t>ロウドウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジカンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>休日労働時間数</t>
+    <rPh sb="0" eb="2">
+      <t>キュウジツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ロウドウ</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ジカンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>残業時間数</t>
+    <rPh sb="0" eb="2">
+      <t>ザンギョウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ジカンスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>控除額</t>
     <rPh sb="0" eb="2">
       <t>コウジョ</t>
@@ -74,6 +117,39 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>健康保険料</t>
+    <rPh sb="0" eb="2">
+      <t>ケンコウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホケンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>厚生年金保険料</t>
+    <rPh sb="0" eb="2">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ネンキン</t>
+    </rPh>
+    <rPh sb="4" eb="7">
+      <t>ホケンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>雇用保険料</t>
+    <rPh sb="0" eb="2">
+      <t>コヨウ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホケンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>性別</t>
     <rPh sb="0" eb="2">
       <t>セイベツ</t>
@@ -97,6 +173,29 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>介護保険料</t>
+    <rPh sb="0" eb="2">
+      <t>カイゴ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ホケンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>控除合計額</t>
+    <rPh sb="0" eb="2">
+      <t>コウジョ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>会社名</t>
     <rPh sb="0" eb="3">
       <t>カイシャメイ</t>
@@ -141,16 +240,6 @@
     <t>給与項目</t>
     <rPh sb="0" eb="2">
       <t>キュウヨ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>賞与項目</t>
-    <rPh sb="0" eb="2">
-      <t>ショウヨ</t>
     </rPh>
     <rPh sb="2" eb="4">
       <t>コウモク</t>
@@ -217,6 +306,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>支給額</t>
+    <rPh sb="0" eb="3">
+      <t>シキュウガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>対象期間</t>
     <rPh sb="0" eb="4">
       <t>タイショウキカン</t>
@@ -224,6 +320,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>厚生年金基金</t>
+    <rPh sb="0" eb="2">
+      <t>コウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ネンキン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>キキン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>社会保険料合計額</t>
     <rPh sb="0" eb="2">
       <t>シャカイ</t>
@@ -240,6 +349,46 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>財形貯蓄</t>
+    <rPh sb="0" eb="4">
+      <t>ザイケイチョチク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>共済費</t>
+    <rPh sb="0" eb="2">
+      <t>キョウサイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>有給取得日数</t>
+    <rPh sb="0" eb="2">
+      <t>ユウキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュトク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>欠勤日数</t>
+    <rPh sb="0" eb="2">
+      <t>ケッキン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>【備考】</t>
     <rPh sb="1" eb="3">
       <t>ビコウ</t>
@@ -247,36 +396,113 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>深夜労働時間数</t>
+  </si>
+  <si>
+    <t>遅刻・早退時間</t>
+    <rPh sb="0" eb="2">
+      <t>チコク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ソウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>源泉所得税</t>
+    <rPh sb="0" eb="5">
+      <t>ゲンセンショトクゼイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>住民税</t>
+    <rPh sb="0" eb="3">
+      <t>ジュウミンゼイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>賞与項目</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>労働保険対象賃金</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>社会保険対象金銭</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>対象額</t>
+    <rPh sb="0" eb="2">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支給控除額</t>
+    <rPh sb="0" eb="2">
+      <t>シキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コウジョ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>非課税支給額</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>課税支給額</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">労働保険対象賃金	</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t xml:space="preserve">社会保険対象賃金	</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>控除合計額</t>
-    <rPh sb="0" eb="2">
+    <t>課税対象額</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>支給合計</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>欠勤控除</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遅早控除</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他控除</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
       <t>コウジョ</t>
     </rPh>
-    <rPh sb="2" eb="5">
-      <t>ゴウケイガク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>支給合計額</t>
-    <rPh sb="2" eb="5">
-      <t>ゴウケイガク</t>
-    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遅刻・早退日数</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>-</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -284,10 +510,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;月&quot;&quot;分&quot;"/>
-    <numFmt numFmtId="178" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -330,7 +555,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="62">
+  <borders count="77">
     <border>
       <left/>
       <right/>
@@ -449,6 +674,19 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -504,6 +742,19 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color indexed="64"/>
       </left>
@@ -704,21 +955,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -869,16 +1105,59 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="hair">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1063,6 +1342,19 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1141,6 +1433,134 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1150,7 +1570,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,311 +1586,422 @@
     <xf numFmtId="38" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="11" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="16" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="57" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="43" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="43" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="46" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="30" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="49" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="51" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="13" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="53" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="54" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="55" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="56" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="62" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="63" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="64" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="62" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="63" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="64" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="17" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="71" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="10" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="15" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="14" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="29" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="26" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="27" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="34" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="31" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="32" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="33" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="36" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="37" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="38" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="39" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="42" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="43" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="44" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="41" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="28" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="18" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="45" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="46" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="47" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="12" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="49" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="50" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="51" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="48" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="52" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="56" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="60" xfId="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="57" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="58" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="59" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1852,1051 +2383,1734 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:AP34"/>
+  <dimension ref="B2:AP46"/>
   <sheetFormatPr defaultRowHeight="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="3.625" customWidth="1"/>
-    <col min="3" max="3" width="21.375" customWidth="1"/>
-    <col min="4" max="22" width="10.125" customWidth="1"/>
+    <col min="2" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="16" width="10.125" customWidth="1"/>
+    <col min="17" max="17" width="4" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
+    <col min="19" max="24" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="92" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="93"/>
-      <c r="K2" s="93"/>
-      <c r="L2" s="93"/>
-      <c r="M2" s="93"/>
-      <c r="N2" s="93"/>
-      <c r="O2" s="93"/>
-      <c r="P2" s="93"/>
-      <c r="Q2" s="93"/>
-      <c r="R2" s="93"/>
-      <c r="S2" s="93"/>
-      <c r="T2" s="93"/>
-      <c r="U2" s="93"/>
-      <c r="V2" s="94"/>
+      <c r="B2" s="118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="119"/>
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="119"/>
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="119"/>
+      <c r="W2" s="119"/>
+      <c r="X2" s="120"/>
     </row>
     <row r="3" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
-      <c r="S3" s="7"/>
-      <c r="T3" s="7"/>
-      <c r="U3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
     </row>
     <row r="4" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="79"/>
-      <c r="D4" s="88"/>
-      <c r="F4" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="79"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="78" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="78" t="s">
-        <v>8</v>
-      </c>
-      <c r="M4" s="79"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="5" t="s">
+      <c r="B4" s="121" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="123"/>
+      <c r="G4" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="103" t="s">
+        <v>15</v>
+      </c>
+      <c r="K4" s="103"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="78" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="S4" s="78" t="s">
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="103" t="s">
         <v>18</v>
       </c>
-      <c r="T4" s="88"/>
-      <c r="U4" s="78" t="s">
-        <v>7</v>
-      </c>
-      <c r="V4" s="88"/>
+      <c r="S4" s="103"/>
+      <c r="T4" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" s="103" t="s">
+        <v>26</v>
+      </c>
+      <c r="V4" s="103"/>
+      <c r="W4" s="103" t="s">
+        <v>16</v>
+      </c>
+      <c r="X4" s="103"/>
     </row>
     <row r="5" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="88"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="78"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="88"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="85"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="85"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="123"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="75"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="110"/>
+      <c r="W5" s="110"/>
+      <c r="X5" s="110"/>
     </row>
     <row r="6" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="101" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="102"/>
-      <c r="L7" s="102"/>
-      <c r="M7" s="102"/>
-      <c r="N7" s="102"/>
-      <c r="O7" s="102"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="101" t="s">
-        <v>11</v>
-      </c>
-      <c r="R7" s="102"/>
-      <c r="S7" s="102"/>
-      <c r="T7" s="102"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="98" t="s">
-        <v>16</v>
+      <c r="B7" s="104" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="105"/>
+      <c r="J7" s="105"/>
+      <c r="K7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="105"/>
+      <c r="P7" s="106"/>
+      <c r="Q7" s="104" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" s="105"/>
+      <c r="S7" s="105"/>
+      <c r="T7" s="105"/>
+      <c r="U7" s="105"/>
+      <c r="V7" s="105"/>
+      <c r="W7" s="106"/>
+      <c r="X7" s="124" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="87"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="106" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="104" t="s">
-        <v>13</v>
-      </c>
-      <c r="V8" s="99"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-    </row>
-    <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="96" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
-      <c r="N9" s="18"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="106"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="18"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="105"/>
-      <c r="V9" s="100"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="6"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="6"/>
-      <c r="AL9" s="6"/>
-      <c r="AM9" s="6"/>
-      <c r="AN9" s="6"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="17"/>
-    </row>
-    <row r="10" spans="2:42" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="95"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="30"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="70">
-        <f t="shared" ref="V10" si="0">P10+U10</f>
+      <c r="B8" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="117"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="129" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" s="108"/>
+      <c r="S8" s="9"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="9"/>
+      <c r="V8" s="10"/>
+      <c r="W8" s="127" t="s">
+        <v>21</v>
+      </c>
+      <c r="X8" s="125"/>
+      <c r="Y8" s="1"/>
+    </row>
+    <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="102"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="129"/>
+      <c r="Q9" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="R9" s="109"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="128"/>
+      <c r="X9" s="126"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="5"/>
+      <c r="AA9" s="5"/>
+      <c r="AB9" s="5"/>
+      <c r="AC9" s="5"/>
+      <c r="AD9" s="5"/>
+      <c r="AE9" s="5"/>
+      <c r="AF9" s="5"/>
+      <c r="AG9" s="5"/>
+      <c r="AH9" s="5"/>
+      <c r="AI9" s="5"/>
+      <c r="AJ9" s="5"/>
+      <c r="AK9" s="5"/>
+      <c r="AL9" s="5"/>
+      <c r="AM9" s="5"/>
+      <c r="AN9" s="5"/>
+      <c r="AO9" s="15"/>
+      <c r="AP9" s="15"/>
+    </row>
+    <row r="10" spans="2:42" ht="17.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="36">
+        <f>SUM(D10:O10)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" s="81" t="s">
+        <v>54</v>
+      </c>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="38"/>
+      <c r="W10" s="39">
+        <f>SUM(S10:V10)</f>
+        <v>0</v>
+      </c>
+      <c r="X10" s="69">
+        <f>P10+W10</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="95"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="32"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="34"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="32"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="70">
-        <f>P11+U11</f>
+      <c r="B11" s="136"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="29">
+        <f t="shared" ref="P11:P34" si="0">SUM(D11:O11)</f>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="136"/>
+      <c r="R11" s="82" t="s">
+        <v>44</v>
+      </c>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="27"/>
+      <c r="W11" s="29">
+        <f t="shared" ref="W11:W36" si="1">SUM(S11:V11)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="93">
+        <f>P11+W11</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="95"/>
-      <c r="C12" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="22"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="23"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="23"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="71">
-        <f t="shared" ref="V12:V17" si="1">P12+U12</f>
+      <c r="B12" s="136"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="82" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" s="26"/>
+      <c r="T12" s="26"/>
+      <c r="U12" s="26"/>
+      <c r="V12" s="27"/>
+      <c r="W12" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X12" s="28">
+        <f t="shared" ref="X12:X36" si="2">P12+W12</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="95"/>
-      <c r="C13" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="38"/>
-      <c r="S13" s="38"/>
-      <c r="T13" s="39"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="72">
-        <f t="shared" si="1"/>
+      <c r="B13" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="44"/>
+      <c r="Q13" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="R13" s="92" t="s">
+        <v>54</v>
+      </c>
+      <c r="S13" s="19"/>
+      <c r="T13" s="19"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="44"/>
+      <c r="X13" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="95"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="22"/>
-      <c r="O14" s="23"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="70">
-        <f t="shared" si="1"/>
+      <c r="C14" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="27"/>
+      <c r="W14" s="29"/>
+      <c r="X14" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="95"/>
-      <c r="C15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="22"/>
-      <c r="K15" s="22"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="22"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="42"/>
-      <c r="V15" s="71">
-        <f t="shared" ref="V15:V16" si="2">P15+U15</f>
+      <c r="C15" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="82" t="s">
+        <v>54</v>
+      </c>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="26"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="29"/>
+      <c r="X15" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="95"/>
-      <c r="C16" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="39"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="38"/>
-      <c r="S16" s="38"/>
-      <c r="T16" s="39"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="72">
+      <c r="B16" s="96"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="96"/>
+      <c r="R16" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="42"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="137" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="138"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="19"/>
+      <c r="N17" s="19"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q17" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="R17" s="98"/>
+      <c r="S17" s="19"/>
+      <c r="T17" s="19"/>
+      <c r="U17" s="19"/>
+      <c r="V17" s="20"/>
+      <c r="W17" s="44">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X17" s="21">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="95"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38"/>
-      <c r="J17" s="38"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="39"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="38"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="70">
+    <row r="18" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="140"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q18" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="R18" s="100"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="43">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="60"/>
-      <c r="C18" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="3">
-        <f>SUM(D10:D11)</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="3">
-        <f t="shared" ref="E18:O18" si="3">SUM(E10:E11)</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="3">
+      <c r="X18" s="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="102"/>
+      <c r="D19" s="87">
+        <f>SUM(D10:D16)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="87">
+        <f t="shared" ref="E19:O19" si="3">SUM(E10:E16)</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O19" s="87">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P18" s="15">
-        <f>SUM(D18:O18)</f>
-        <v>0</v>
-      </c>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="15">
-        <f>SUM(R18:T18)</f>
-        <v>0</v>
-      </c>
-      <c r="V18" s="73">
-        <f>P18+U18</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="82" t="s">
+      <c r="P19" s="88">
+        <f>SUM(D19:O19)</f>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="R19" s="102"/>
+      <c r="S19" s="3">
+        <f>SUM(S10:S16)</f>
+        <v>0</v>
+      </c>
+      <c r="T19" s="3">
+        <f t="shared" ref="T19:V19" si="4">SUM(T10:T16)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V19" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W19" s="11">
+        <f>SUM(S19:V19)</f>
+        <v>0</v>
+      </c>
+      <c r="X19" s="76">
+        <f>P19+W19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="132" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="20"/>
+      <c r="P20" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="89"/>
+      <c r="R20" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="S20" s="86" t="s">
+        <v>44</v>
+      </c>
+      <c r="T20" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="U20" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="V20" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="133"/>
+      <c r="C21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="11">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="90"/>
+      <c r="R21" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="S21" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="T21" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="U21" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="V21" s="78" t="s">
+        <v>43</v>
+      </c>
+      <c r="W21" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="X21" s="76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="111" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="65"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="111" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="84" t="s">
+        <v>7</v>
+      </c>
+      <c r="S22" s="65"/>
+      <c r="T22" s="65"/>
+      <c r="U22" s="65"/>
+      <c r="V22" s="66"/>
+      <c r="W22" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X22" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="95"/>
+      <c r="C23" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="95"/>
+      <c r="R23" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="26"/>
+      <c r="V23" s="27"/>
+      <c r="W23" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X23" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="95"/>
+      <c r="C24" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="95"/>
+      <c r="R24" s="82" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="26"/>
+      <c r="V24" s="27"/>
+      <c r="W24" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X24" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="95"/>
+      <c r="C25" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q25" s="95"/>
+      <c r="R25" s="82" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X25" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="95"/>
+      <c r="C26" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="95"/>
+      <c r="R26" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="26"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="95"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="95"/>
+      <c r="R27" s="85"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X27" s="62">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="95"/>
+      <c r="C28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="3">
+        <f>SUM(D22:D26)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="3">
+        <f t="shared" ref="E28:O28" si="5">SUM(E22:E26)</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="L28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="P28" s="11">
+        <f>SUM(D28:O28)</f>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="95"/>
+      <c r="R28" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="S28" s="3">
+        <f>SUM(S22:S26)</f>
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <f t="shared" ref="T28:V28" si="6">SUM(T22:T26)</f>
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="W28" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X28" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="95"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="65"/>
+      <c r="E29" s="65"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
+      <c r="H29" s="65"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="65"/>
+      <c r="K29" s="65"/>
+      <c r="L29" s="65"/>
+      <c r="M29" s="65"/>
+      <c r="N29" s="65"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q29" s="95"/>
+      <c r="R29" s="84"/>
+      <c r="S29" s="65"/>
+      <c r="T29" s="65"/>
+      <c r="U29" s="65"/>
+      <c r="V29" s="66"/>
+      <c r="W29" s="67">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X29" s="68">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="95"/>
+      <c r="C30" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="27"/>
+      <c r="P30" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q30" s="95"/>
+      <c r="R30" s="82" t="s">
+        <v>39</v>
+      </c>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="27"/>
+      <c r="W30" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X30" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="95"/>
+      <c r="C31" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="95"/>
+      <c r="R31" s="82" t="s">
+        <v>38</v>
+      </c>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="27"/>
+      <c r="W31" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X31" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="95"/>
+      <c r="C32" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q32" s="95"/>
+      <c r="R32" s="82"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="27"/>
+      <c r="W32" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X32" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="95"/>
+      <c r="C33" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q33" s="95"/>
+      <c r="R33" s="82"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="27"/>
+      <c r="W33" s="29">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X33" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="112"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="41"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q34" s="112"/>
+      <c r="R34" s="83"/>
+      <c r="S34" s="41"/>
+      <c r="T34" s="41"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="43">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X34" s="33">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="117"/>
+      <c r="D35" s="4">
+        <f>SUM(D30:D33)+D28</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="4">
+        <f t="shared" ref="E35:O35" si="7">SUM(E30:E33)+E28</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="L35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O35" s="4">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P35" s="11">
+        <f>SUM(D35:O35)</f>
+        <v>0</v>
+      </c>
+      <c r="Q35" s="113" t="s">
+        <v>13</v>
+      </c>
+      <c r="R35" s="108"/>
+      <c r="S35" s="3">
+        <f>SUM(S30:S31)+S28</f>
+        <v>0</v>
+      </c>
+      <c r="T35" s="3">
+        <f t="shared" ref="T35:V35" si="8">SUM(T30:T31)+T28</f>
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="V35" s="3">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="W35" s="11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X35" s="13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B36" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="116"/>
+      <c r="D36" s="7">
+        <f>D19-D35</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <f t="shared" ref="E36:O36" si="9">E19-E35</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="K36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O36" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P36" s="12">
+        <f>SUM(D36:O36)</f>
+        <v>0</v>
+      </c>
+      <c r="Q36" s="114" t="s">
+        <v>6</v>
+      </c>
+      <c r="R36" s="115"/>
+      <c r="S36" s="7">
+        <f>S19-S35</f>
+        <v>0</v>
+      </c>
+      <c r="T36" s="7">
+        <f t="shared" ref="T36:V36" si="10">T19-T35</f>
+        <v>0</v>
+      </c>
+      <c r="U36" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="V36" s="7">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="W36" s="12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="X36" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="141" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29"/>
-      <c r="O19" s="30"/>
-      <c r="P19" s="31"/>
-      <c r="Q19" s="28"/>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="74">
-        <f t="shared" ref="V19:V23" si="4">P19+U19</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="83"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="74">
-        <f>P20+U20</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="83"/>
-      <c r="C21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="3">
-        <f>SUM(D19:D20)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <f t="shared" ref="E21:O21" si="5">SUM(E19:E20)</f>
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="3">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="15">
-        <f>SUM(D21:O21)</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="3"/>
-      <c r="S21" s="3"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="15"/>
-      <c r="V21" s="73">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="83"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="62"/>
-      <c r="E22" s="62"/>
-      <c r="F22" s="62"/>
-      <c r="G22" s="62"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="62"/>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="64"/>
-      <c r="V22" s="75">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="83"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="74">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="86" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="87"/>
-      <c r="D24" s="4">
-        <f t="shared" ref="D24:O24" si="6">SUM(D21:D23)</f>
-        <v>0</v>
-      </c>
-      <c r="E24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="I24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="4">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="15">
-        <f>SUM(D24:O24)</f>
-        <v>0</v>
-      </c>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="15">
-        <f>SUM(Q24:T24)</f>
-        <v>0</v>
-      </c>
-      <c r="V24" s="73">
-        <f>P24+U24</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="80" t="s">
+      <c r="D38" s="50"/>
+      <c r="E38" s="50"/>
+      <c r="F38" s="50"/>
+      <c r="G38" s="50"/>
+      <c r="H38" s="50"/>
+      <c r="I38" s="50"/>
+      <c r="J38" s="50"/>
+      <c r="K38" s="50"/>
+      <c r="L38" s="50"/>
+      <c r="M38" s="50"/>
+      <c r="N38" s="50"/>
+      <c r="O38" s="51"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="R38" s="131"/>
+      <c r="S38" s="73"/>
+      <c r="T38" s="53"/>
+      <c r="U38" s="53"/>
+      <c r="V38" s="53"/>
+      <c r="W38" s="54"/>
+      <c r="X38" s="8"/>
+    </row>
+    <row r="39" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="142"/>
+      <c r="C39" s="64" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="70"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="72"/>
+      <c r="Q39" s="74"/>
+      <c r="R39" s="47"/>
+      <c r="S39" s="46"/>
+      <c r="T39" s="46"/>
+      <c r="U39" s="46"/>
+      <c r="V39" s="46"/>
+      <c r="W39" s="47"/>
+      <c r="X39" s="48"/>
+    </row>
+    <row r="40" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="142"/>
+      <c r="C40" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="70"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="72"/>
+      <c r="Q40" s="74"/>
+      <c r="R40" s="47"/>
+      <c r="S40" s="46"/>
+      <c r="T40" s="46"/>
+      <c r="U40" s="46"/>
+      <c r="V40" s="46"/>
+      <c r="W40" s="47"/>
+      <c r="X40" s="48"/>
+    </row>
+    <row r="41" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="142"/>
+      <c r="C41" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="70"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="70"/>
+      <c r="L41" s="70"/>
+      <c r="M41" s="70"/>
+      <c r="N41" s="70"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="72"/>
+      <c r="Q41" s="74"/>
+      <c r="R41" s="47"/>
+      <c r="S41" s="46"/>
+      <c r="T41" s="46"/>
+      <c r="U41" s="46"/>
+      <c r="V41" s="46"/>
+      <c r="W41" s="47"/>
+      <c r="X41" s="48"/>
+    </row>
+    <row r="42" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="142"/>
+      <c r="C42" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="81"/>
-      <c r="D25" s="8">
-        <f>SUM(D18-D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="8">
-        <f t="shared" ref="D25:O25" si="7">SUM(E18-E24)</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="G25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="H25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="8">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="16">
-        <f>SUM(D25:O25)</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="10"/>
-      <c r="R25" s="3"/>
-      <c r="S25" s="3"/>
-      <c r="T25" s="14"/>
-      <c r="U25" s="16">
-        <f>SUM(Q25:T25)</f>
-        <v>0</v>
-      </c>
-      <c r="V25" s="76">
-        <f>P25+U25</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="89" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="69" t="s">
-        <v>21</v>
-      </c>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="51"/>
-      <c r="V27" s="9"/>
-    </row>
-    <row r="28" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="90"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="66"/>
-      <c r="E28" s="66"/>
-      <c r="F28" s="66"/>
-      <c r="G28" s="66"/>
-      <c r="H28" s="66"/>
-      <c r="I28" s="66"/>
-      <c r="J28" s="66"/>
-      <c r="K28" s="66"/>
-      <c r="L28" s="66"/>
-      <c r="M28" s="66"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="67"/>
-      <c r="P28" s="68"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="77"/>
-      <c r="S28" s="77"/>
-      <c r="T28" s="77"/>
-      <c r="U28" s="77"/>
-      <c r="V28" s="45"/>
-    </row>
-    <row r="29" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="90"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="66"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-      <c r="M29" s="66"/>
-      <c r="N29" s="66"/>
-      <c r="O29" s="67"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="77"/>
-      <c r="S29" s="77"/>
-      <c r="T29" s="77"/>
-      <c r="U29" s="77"/>
-      <c r="V29" s="45"/>
-    </row>
-    <row r="30" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="90"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="26"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="77"/>
-      <c r="S30" s="77"/>
-      <c r="T30" s="77"/>
-      <c r="U30" s="77"/>
-      <c r="V30" s="45"/>
-    </row>
-    <row r="31" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="90"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="31"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="77"/>
-      <c r="S31" s="77"/>
-      <c r="T31" s="77"/>
-      <c r="U31" s="77"/>
-      <c r="V31" s="45"/>
-    </row>
-    <row r="32" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="90"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="77"/>
-      <c r="S32" s="77"/>
-      <c r="T32" s="77"/>
-      <c r="U32" s="77"/>
-      <c r="V32" s="45"/>
-    </row>
-    <row r="33" spans="2:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="90"/>
-      <c r="C33" s="59"/>
-      <c r="D33" s="32"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="32"/>
-      <c r="G33" s="32"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="32"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="77"/>
-      <c r="S33" s="77"/>
-      <c r="T33" s="77"/>
-      <c r="U33" s="77"/>
-      <c r="V33" s="45"/>
-    </row>
-    <row r="34" spans="2:22" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="91"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
-      <c r="H34" s="53"/>
-      <c r="I34" s="53"/>
-      <c r="J34" s="53"/>
-      <c r="K34" s="53"/>
-      <c r="L34" s="53"/>
-      <c r="M34" s="53"/>
-      <c r="N34" s="53"/>
-      <c r="O34" s="54"/>
-      <c r="P34" s="55"/>
-      <c r="Q34" s="56"/>
-      <c r="R34" s="57"/>
-      <c r="S34" s="57"/>
-      <c r="T34" s="57"/>
-      <c r="U34" s="57"/>
-      <c r="V34" s="58"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="25"/>
+      <c r="Q42" s="74"/>
+      <c r="R42" s="47"/>
+      <c r="S42" s="46"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="47"/>
+      <c r="X42" s="48"/>
+    </row>
+    <row r="43" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="142"/>
+      <c r="C43" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="27"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="45"/>
+      <c r="R43" s="46"/>
+      <c r="S43" s="46"/>
+      <c r="T43" s="46"/>
+      <c r="U43" s="46"/>
+      <c r="V43" s="46"/>
+      <c r="W43" s="46"/>
+      <c r="X43" s="48"/>
+    </row>
+    <row r="44" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="142"/>
+      <c r="C44" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="29"/>
+      <c r="Q44" s="45"/>
+      <c r="R44" s="46"/>
+      <c r="S44" s="46"/>
+      <c r="T44" s="46"/>
+      <c r="U44" s="46"/>
+      <c r="V44" s="46"/>
+      <c r="W44" s="46"/>
+      <c r="X44" s="48"/>
+    </row>
+    <row r="45" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="142"/>
+      <c r="C45" s="61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="30"/>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+      <c r="G45" s="30"/>
+      <c r="H45" s="30"/>
+      <c r="I45" s="30"/>
+      <c r="J45" s="30"/>
+      <c r="K45" s="30"/>
+      <c r="L45" s="30"/>
+      <c r="M45" s="30"/>
+      <c r="N45" s="30"/>
+      <c r="O45" s="31"/>
+      <c r="P45" s="32"/>
+      <c r="Q45" s="45"/>
+      <c r="R45" s="46"/>
+      <c r="S45" s="46"/>
+      <c r="T45" s="46"/>
+      <c r="U45" s="46"/>
+      <c r="V45" s="46"/>
+      <c r="W45" s="46"/>
+      <c r="X45" s="48"/>
+    </row>
+    <row r="46" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B46" s="143"/>
+      <c r="C46" s="91" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="55"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="55"/>
+      <c r="N46" s="55"/>
+      <c r="O46" s="56"/>
+      <c r="P46" s="57"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="59"/>
+      <c r="S46" s="59"/>
+      <c r="T46" s="59"/>
+      <c r="U46" s="59"/>
+      <c r="V46" s="59"/>
+      <c r="W46" s="59"/>
+      <c r="X46" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="B2:V2"/>
-    <mergeCell ref="B10:B17"/>
+  <mergeCells count="45">
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="M5:O5"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="Q10:Q12"/>
+    <mergeCell ref="B38:B46"/>
+    <mergeCell ref="B2:X2"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="X7:X9"/>
     <mergeCell ref="B7:P7"/>
-    <mergeCell ref="Q7:U7"/>
-    <mergeCell ref="U8:U9"/>
+    <mergeCell ref="W8:W9"/>
     <mergeCell ref="P8:P9"/>
-    <mergeCell ref="R28:U33"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="U5:V5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="Q22:Q34"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B22:B34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="Q13:Q16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
     <mergeCell ref="U4:V4"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="B27:B34"/>
+    <mergeCell ref="Q7:W7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W5:X5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.27559055118110237" right="0.11811023622047245" top="0.27559055118110237" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="67" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" orientation="landscape" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
--- a/storage/app/wage-template/ledger-format.xlsx
+++ b/storage/app/wage-template/ledger-format.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\devbox\karte\dev_docker\app\karte\storage\app\wage-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9251A38-492C-4579-9AA0-B161FDB61752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D03F53-7A1E-4FE2-AE59-693695234299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-795" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-36840" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="4" r:id="rId1"/>
@@ -514,7 +514,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;月&quot;&quot;分&quot;"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ 明朝"/>
@@ -540,6 +540,12 @@
       <family val="1"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1853,6 +1859,24 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1862,6 +1886,108 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
@@ -1874,133 +2000,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="59" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
@@ -2395,31 +2401,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="118" t="s">
+      <c r="B2" s="112" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="119"/>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="120"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="114"/>
     </row>
     <row r="3" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="6"/>
@@ -2446,106 +2452,106 @@
       <c r="W3" s="6"/>
     </row>
     <row r="4" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="115" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="122"/>
-      <c r="D4" s="123"/>
-      <c r="G4" s="103" t="s">
+      <c r="C4" s="116"/>
+      <c r="D4" s="117"/>
+      <c r="G4" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="103"/>
-      <c r="I4" s="103"/>
-      <c r="J4" s="103" t="s">
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="96" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="103"/>
-      <c r="L4" s="103"/>
-      <c r="M4" s="103" t="s">
+      <c r="K4" s="96"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="96" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="103"/>
-      <c r="O4" s="103"/>
-      <c r="P4" s="103" t="s">
+      <c r="N4" s="96"/>
+      <c r="O4" s="96"/>
+      <c r="P4" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="103"/>
-      <c r="R4" s="103" t="s">
+      <c r="Q4" s="96"/>
+      <c r="R4" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="103"/>
+      <c r="S4" s="96"/>
       <c r="T4" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="103" t="s">
+      <c r="U4" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="103"/>
-      <c r="W4" s="103" t="s">
+      <c r="V4" s="96"/>
+      <c r="W4" s="96" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="103"/>
+      <c r="X4" s="96"/>
     </row>
     <row r="5" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="121"/>
-      <c r="C5" s="122"/>
-      <c r="D5" s="123"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
+      <c r="B5" s="115"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="117"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
       <c r="T5" s="75"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="110"/>
-      <c r="W5" s="110"/>
-      <c r="X5" s="110"/>
+      <c r="U5" s="127"/>
+      <c r="V5" s="127"/>
+      <c r="W5" s="127"/>
+      <c r="X5" s="127"/>
     </row>
     <row r="6" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="105"/>
-      <c r="J7" s="105"/>
-      <c r="K7" s="105"/>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="105"/>
-      <c r="P7" s="106"/>
-      <c r="Q7" s="104" t="s">
+      <c r="C7" s="122"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="122"/>
+      <c r="F7" s="122"/>
+      <c r="G7" s="122"/>
+      <c r="H7" s="122"/>
+      <c r="I7" s="122"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
+      <c r="N7" s="122"/>
+      <c r="O7" s="122"/>
+      <c r="P7" s="123"/>
+      <c r="Q7" s="121" t="s">
         <v>40</v>
       </c>
-      <c r="R7" s="105"/>
-      <c r="S7" s="105"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="105"/>
-      <c r="V7" s="105"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="124" t="s">
+      <c r="R7" s="122"/>
+      <c r="S7" s="122"/>
+      <c r="T7" s="122"/>
+      <c r="U7" s="122"/>
+      <c r="V7" s="122"/>
+      <c r="W7" s="123"/>
+      <c r="X7" s="118" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="117"/>
+      <c r="B8" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="129"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2558,28 +2564,28 @@
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="129" t="s">
+      <c r="P8" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="R8" s="108"/>
+      <c r="Q8" s="128" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" s="133"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
       <c r="V8" s="10"/>
-      <c r="W8" s="127" t="s">
+      <c r="W8" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="125"/>
+      <c r="X8" s="119"/>
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="101" t="s">
+      <c r="B9" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="102"/>
+      <c r="C9" s="108"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
@@ -2592,17 +2598,17 @@
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="17"/>
-      <c r="P9" s="129"/>
-      <c r="Q9" s="101" t="s">
+      <c r="P9" s="126"/>
+      <c r="Q9" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="109"/>
+      <c r="R9" s="141"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
       <c r="V9" s="17"/>
-      <c r="W9" s="128"/>
-      <c r="X9" s="126"/>
+      <c r="W9" s="125"/>
+      <c r="X9" s="120"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
@@ -2623,7 +2629,7 @@
       <c r="AP9" s="15"/>
     </row>
     <row r="10" spans="2:42" ht="17.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="135" t="s">
+      <c r="B10" s="98" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="63"/>
@@ -2643,7 +2649,7 @@
         <f>SUM(D10:O10)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="135" t="s">
+      <c r="Q10" s="98" t="s">
         <v>27</v>
       </c>
       <c r="R10" s="81" t="s">
@@ -2663,7 +2669,7 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="136"/>
+      <c r="B11" s="99"/>
       <c r="C11" s="22"/>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
@@ -2681,7 +2687,7 @@
         <f t="shared" ref="P11:P34" si="0">SUM(D11:O11)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="136"/>
+      <c r="Q11" s="99"/>
       <c r="R11" s="82" t="s">
         <v>44</v>
       </c>
@@ -2699,7 +2705,7 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="136"/>
+      <c r="B12" s="99"/>
       <c r="C12" s="22"/>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
@@ -2717,7 +2723,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="136"/>
+      <c r="Q12" s="99"/>
       <c r="R12" s="82" t="s">
         <v>43</v>
       </c>
@@ -2735,7 +2741,7 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="100" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -2754,7 +2760,7 @@
       <c r="N13" s="19"/>
       <c r="O13" s="20"/>
       <c r="P13" s="44"/>
-      <c r="Q13" s="94" t="s">
+      <c r="Q13" s="100" t="s">
         <v>46</v>
       </c>
       <c r="R13" s="92" t="s">
@@ -2770,7 +2776,7 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="95"/>
+      <c r="B14" s="101"/>
       <c r="C14" s="22" t="s">
         <v>51</v>
       </c>
@@ -2787,7 +2793,7 @@
       <c r="N14" s="26"/>
       <c r="O14" s="27"/>
       <c r="P14" s="29"/>
-      <c r="Q14" s="95"/>
+      <c r="Q14" s="101"/>
       <c r="R14" s="82" t="s">
         <v>54</v>
       </c>
@@ -2801,7 +2807,7 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="95"/>
+      <c r="B15" s="101"/>
       <c r="C15" s="22" t="s">
         <v>52</v>
       </c>
@@ -2818,7 +2824,7 @@
       <c r="N15" s="26"/>
       <c r="O15" s="27"/>
       <c r="P15" s="29"/>
-      <c r="Q15" s="95"/>
+      <c r="Q15" s="101"/>
       <c r="R15" s="82" t="s">
         <v>54</v>
       </c>
@@ -2832,7 +2838,7 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="96"/>
+      <c r="B16" s="102"/>
       <c r="C16" s="40"/>
       <c r="D16" s="41"/>
       <c r="E16" s="41"/>
@@ -2847,7 +2853,7 @@
       <c r="N16" s="41"/>
       <c r="O16" s="42"/>
       <c r="P16" s="43"/>
-      <c r="Q16" s="96"/>
+      <c r="Q16" s="102"/>
       <c r="R16" s="83" t="s">
         <v>54</v>
       </c>
@@ -2861,10 +2867,10 @@
       </c>
     </row>
     <row r="17" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="137" t="s">
+      <c r="B17" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="138"/>
+      <c r="C17" s="104"/>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
       <c r="F17" s="19"/>
@@ -2881,10 +2887,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="97" t="s">
+      <c r="Q17" s="137" t="s">
         <v>47</v>
       </c>
-      <c r="R17" s="98"/>
+      <c r="R17" s="138"/>
       <c r="S17" s="19"/>
       <c r="T17" s="19"/>
       <c r="U17" s="19"/>
@@ -2899,10 +2905,10 @@
       </c>
     </row>
     <row r="18" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="139" t="s">
+      <c r="B18" s="105" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="140"/>
+      <c r="C18" s="106"/>
       <c r="D18" s="41"/>
       <c r="E18" s="41"/>
       <c r="F18" s="41"/>
@@ -2919,10 +2925,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="99" t="s">
+      <c r="Q18" s="139" t="s">
         <v>48</v>
       </c>
-      <c r="R18" s="100"/>
+      <c r="R18" s="140"/>
       <c r="S18" s="41"/>
       <c r="T18" s="41"/>
       <c r="U18" s="41"/>
@@ -2937,10 +2943,10 @@
       </c>
     </row>
     <row r="19" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="101" t="s">
+      <c r="B19" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="102"/>
+      <c r="C19" s="108"/>
       <c r="D19" s="87">
         <f>SUM(D10:D16)</f>
         <v>0</v>
@@ -2993,10 +2999,10 @@
         <f>SUM(D19:O19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="101" t="s">
+      <c r="Q19" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="R19" s="102"/>
+      <c r="R19" s="108"/>
       <c r="S19" s="3">
         <f>SUM(S10:S16)</f>
         <v>0</v>
@@ -3023,7 +3029,7 @@
       </c>
     </row>
     <row r="20" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="142" t="s">
         <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -3068,7 +3074,7 @@
       </c>
     </row>
     <row r="21" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="133"/>
+      <c r="B21" s="143"/>
       <c r="C21" s="2" t="s">
         <v>42</v>
       </c>
@@ -3111,7 +3117,7 @@
       </c>
     </row>
     <row r="22" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="111" t="s">
+      <c r="B22" s="130" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="64" t="s">
@@ -3133,7 +3139,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="111" t="s">
+      <c r="Q22" s="130" t="s">
         <v>5</v>
       </c>
       <c r="R22" s="84" t="s">
@@ -3153,7 +3159,7 @@
       </c>
     </row>
     <row r="23" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="95"/>
+      <c r="B23" s="101"/>
       <c r="C23" s="22" t="s">
         <v>12</v>
       </c>
@@ -3173,7 +3179,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="95"/>
+      <c r="Q23" s="101"/>
       <c r="R23" s="82" t="s">
         <v>12</v>
       </c>
@@ -3191,7 +3197,7 @@
       </c>
     </row>
     <row r="24" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="95"/>
+      <c r="B24" s="101"/>
       <c r="C24" s="22" t="s">
         <v>8</v>
       </c>
@@ -3211,7 +3217,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="95"/>
+      <c r="Q24" s="101"/>
       <c r="R24" s="82" t="s">
         <v>8</v>
       </c>
@@ -3229,7 +3235,7 @@
       </c>
     </row>
     <row r="25" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="95"/>
+      <c r="B25" s="101"/>
       <c r="C25" s="22" t="s">
         <v>29</v>
       </c>
@@ -3249,7 +3255,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="95"/>
+      <c r="Q25" s="101"/>
       <c r="R25" s="82" t="s">
         <v>29</v>
       </c>
@@ -3267,7 +3273,7 @@
       </c>
     </row>
     <row r="26" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="95"/>
+      <c r="B26" s="101"/>
       <c r="C26" s="22" t="s">
         <v>9</v>
       </c>
@@ -3287,7 +3293,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="95"/>
+      <c r="Q26" s="101"/>
       <c r="R26" s="82" t="s">
         <v>9</v>
       </c>
@@ -3305,7 +3311,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="95"/>
+      <c r="B27" s="101"/>
       <c r="C27" s="61"/>
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
@@ -3323,7 +3329,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="95"/>
+      <c r="Q27" s="101"/>
       <c r="R27" s="85"/>
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
@@ -3339,7 +3345,7 @@
       </c>
     </row>
     <row r="28" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="95"/>
+      <c r="B28" s="101"/>
       <c r="C28" s="2" t="s">
         <v>30</v>
       </c>
@@ -3395,7 +3401,7 @@
         <f>SUM(D28:O28)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="95"/>
+      <c r="Q28" s="101"/>
       <c r="R28" s="80" t="s">
         <v>30</v>
       </c>
@@ -3425,7 +3431,7 @@
       </c>
     </row>
     <row r="29" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="95"/>
+      <c r="B29" s="101"/>
       <c r="C29" s="64"/>
       <c r="D29" s="65"/>
       <c r="E29" s="65"/>
@@ -3443,7 +3449,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="95"/>
+      <c r="Q29" s="101"/>
       <c r="R29" s="84"/>
       <c r="S29" s="65"/>
       <c r="T29" s="65"/>
@@ -3459,7 +3465,7 @@
       </c>
     </row>
     <row r="30" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="95"/>
+      <c r="B30" s="101"/>
       <c r="C30" s="22" t="s">
         <v>39</v>
       </c>
@@ -3479,7 +3485,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="95"/>
+      <c r="Q30" s="101"/>
       <c r="R30" s="82" t="s">
         <v>39</v>
       </c>
@@ -3497,7 +3503,7 @@
       </c>
     </row>
     <row r="31" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="95"/>
+      <c r="B31" s="101"/>
       <c r="C31" s="22" t="s">
         <v>38</v>
       </c>
@@ -3517,7 +3523,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="95"/>
+      <c r="Q31" s="101"/>
       <c r="R31" s="82" t="s">
         <v>38</v>
       </c>
@@ -3535,7 +3541,7 @@
       </c>
     </row>
     <row r="32" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="95"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="22" t="s">
         <v>32</v>
       </c>
@@ -3555,7 +3561,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="95"/>
+      <c r="Q32" s="101"/>
       <c r="R32" s="82"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
@@ -3571,7 +3577,7 @@
       </c>
     </row>
     <row r="33" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="95"/>
+      <c r="B33" s="101"/>
       <c r="C33" s="22" t="s">
         <v>31</v>
       </c>
@@ -3591,7 +3597,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="95"/>
+      <c r="Q33" s="101"/>
       <c r="R33" s="82"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
@@ -3607,7 +3613,7 @@
       </c>
     </row>
     <row r="34" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="112"/>
+      <c r="B34" s="131"/>
       <c r="C34" s="40"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
@@ -3625,7 +3631,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="112"/>
+      <c r="Q34" s="131"/>
       <c r="R34" s="83"/>
       <c r="S34" s="41"/>
       <c r="T34" s="41"/>
@@ -3641,10 +3647,10 @@
       </c>
     </row>
     <row r="35" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="113" t="s">
+      <c r="B35" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="117"/>
+      <c r="C35" s="129"/>
       <c r="D35" s="4">
         <f>SUM(D30:D33)+D28</f>
         <v>0</v>
@@ -3697,10 +3703,10 @@
         <f>SUM(D35:O35)</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="113" t="s">
+      <c r="Q35" s="132" t="s">
         <v>13</v>
       </c>
-      <c r="R35" s="108"/>
+      <c r="R35" s="133"/>
       <c r="S35" s="3">
         <f>SUM(S30:S31)+S28</f>
         <v>0</v>
@@ -3727,10 +3733,10 @@
       </c>
     </row>
     <row r="36" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="114" t="s">
+      <c r="B36" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="116"/>
+      <c r="C36" s="136"/>
       <c r="D36" s="7">
         <f>D19-D35</f>
         <v>0</v>
@@ -3783,10 +3789,10 @@
         <f>SUM(D36:O36)</f>
         <v>0</v>
       </c>
-      <c r="Q36" s="114" t="s">
+      <c r="Q36" s="134" t="s">
         <v>6</v>
       </c>
-      <c r="R36" s="115"/>
+      <c r="R36" s="135"/>
       <c r="S36" s="7">
         <f>S19-S35</f>
         <v>0</v>
@@ -3814,7 +3820,7 @@
     </row>
     <row r="37" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="38" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="141" t="s">
+      <c r="B38" s="109" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="49" t="s">
@@ -3833,10 +3839,10 @@
       <c r="N38" s="50"/>
       <c r="O38" s="51"/>
       <c r="P38" s="52"/>
-      <c r="Q38" s="130" t="s">
+      <c r="Q38" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="R38" s="131"/>
+      <c r="R38" s="95"/>
       <c r="S38" s="73"/>
       <c r="T38" s="53"/>
       <c r="U38" s="53"/>
@@ -3845,7 +3851,7 @@
       <c r="X38" s="8"/>
     </row>
     <row r="39" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="142"/>
+      <c r="B39" s="110"/>
       <c r="C39" s="64" t="s">
         <v>33</v>
       </c>
@@ -3872,7 +3878,7 @@
       <c r="X39" s="48"/>
     </row>
     <row r="40" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="142"/>
+      <c r="B40" s="110"/>
       <c r="C40" s="64" t="s">
         <v>34</v>
       </c>
@@ -3899,7 +3905,7 @@
       <c r="X40" s="48"/>
     </row>
     <row r="41" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="142"/>
+      <c r="B41" s="110"/>
       <c r="C41" s="64" t="s">
         <v>53</v>
       </c>
@@ -3926,7 +3932,7 @@
       <c r="X41" s="48"/>
     </row>
     <row r="42" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="142"/>
+      <c r="B42" s="110"/>
       <c r="C42" s="22" t="s">
         <v>2</v>
       </c>
@@ -3953,7 +3959,7 @@
       <c r="X42" s="48"/>
     </row>
     <row r="43" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="142"/>
+      <c r="B43" s="110"/>
       <c r="C43" s="22" t="s">
         <v>3</v>
       </c>
@@ -3980,7 +3986,7 @@
       <c r="X43" s="48"/>
     </row>
     <row r="44" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="142"/>
+      <c r="B44" s="110"/>
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -4007,7 +4013,7 @@
       <c r="X44" s="48"/>
     </row>
     <row r="45" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="142"/>
+      <c r="B45" s="110"/>
       <c r="C45" s="61" t="s">
         <v>36</v>
       </c>
@@ -4034,7 +4040,7 @@
       <c r="X45" s="48"/>
     </row>
     <row r="46" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="143"/>
+      <c r="B46" s="111"/>
       <c r="C46" s="91" t="s">
         <v>37</v>
       </c>
@@ -4062,6 +4068,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="Q13:Q16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="Q7:W7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Q22:Q34"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B22:B34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B2:X2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="B7:P7"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="Q38:R38"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="R4:S4"/>
@@ -4078,35 +4113,6 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="B38:B46"/>
-    <mergeCell ref="B2:X2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="B7:P7"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="Q22:Q34"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B22:B34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="Q13:Q16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="Q7:W7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="W5:X5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.27559055118110237" right="0.11811023622047245" top="0.27559055118110237" bottom="0.19685039370078741" header="0" footer="0"/>

--- a/storage/app/wage-template/ledger-format.xlsx
+++ b/storage/app/wage-template/ledger-format.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\devbox\karte\dev_docker\app\karte\storage\app\wage-template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D03F53-7A1E-4FE2-AE59-693695234299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD2C2AF-4FEB-4DBD-B015-56AA2335CCD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36840" yWindow="1560" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base" sheetId="4" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
   <si>
     <t>賃金計算期間</t>
     <rPh sb="0" eb="2">
@@ -345,23 +345,6 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>ガク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>財形貯蓄</t>
-    <rPh sb="0" eb="4">
-      <t>ザイケイチョチク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>共済費</t>
-    <rPh sb="0" eb="2">
-      <t>キョウサイ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ヒ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -514,7 +497,7 @@
     <numFmt numFmtId="176" formatCode="[$-411]ggge&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
     <numFmt numFmtId="177" formatCode="0&quot;月&quot;&quot;分&quot;"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ 明朝"/>
@@ -541,7 +524,13 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
+      <name val="ＭＳ 明朝"/>
+      <family val="1"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="ＭＳ 明朝"/>
       <family val="1"/>
       <charset val="128"/>
@@ -561,7 +550,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="77">
+  <borders count="75">
     <border>
       <left/>
       <right/>
@@ -1481,7 +1470,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1489,30 +1480,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1576,7 +1543,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1838,7 +1805,7 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="1" fillId="0" borderId="71" xfId="1" applyBorder="1">
+    <xf numFmtId="38" fontId="1" fillId="0" borderId="70" xfId="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="1" fillId="0" borderId="19" xfId="1" applyBorder="1">
@@ -1859,15 +1826,114 @@
     <xf numFmtId="38" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1877,33 +1943,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="69" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="74" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -1913,100 +1952,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="70" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
@@ -2401,31 +2359,31 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="113"/>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="114"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="118"/>
     </row>
     <row r="3" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="6"/>
@@ -2452,106 +2410,106 @@
       <c r="W3" s="6"/>
     </row>
     <row r="4" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="115" t="s">
+      <c r="B4" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="116"/>
-      <c r="D4" s="117"/>
-      <c r="G4" s="96" t="s">
+      <c r="C4" s="120"/>
+      <c r="D4" s="121"/>
+      <c r="G4" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="96"/>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96" t="s">
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="101" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96" t="s">
+      <c r="K4" s="101"/>
+      <c r="L4" s="101"/>
+      <c r="M4" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96" t="s">
+      <c r="N4" s="101"/>
+      <c r="O4" s="101"/>
+      <c r="P4" s="101" t="s">
         <v>25</v>
       </c>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="96" t="s">
+      <c r="Q4" s="101"/>
+      <c r="R4" s="101" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="96"/>
+      <c r="S4" s="101"/>
       <c r="T4" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="U4" s="96" t="s">
+      <c r="U4" s="101" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="96"/>
-      <c r="W4" s="96" t="s">
+      <c r="V4" s="101"/>
+      <c r="W4" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="96"/>
+      <c r="X4" s="101"/>
     </row>
     <row r="5" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="115"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="117"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="97"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="120"/>
+      <c r="D5" s="121"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="101"/>
+      <c r="J5" s="101"/>
+      <c r="K5" s="101"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="101"/>
+      <c r="P5" s="130"/>
+      <c r="Q5" s="130"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
       <c r="T5" s="75"/>
-      <c r="U5" s="127"/>
-      <c r="V5" s="127"/>
-      <c r="W5" s="127"/>
-      <c r="X5" s="127"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
     </row>
     <row r="6" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="121" t="s">
+      <c r="B7" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="122"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="122"/>
-      <c r="G7" s="122"/>
-      <c r="H7" s="122"/>
-      <c r="I7" s="122"/>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-      <c r="N7" s="122"/>
-      <c r="O7" s="122"/>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="121" t="s">
-        <v>40</v>
-      </c>
-      <c r="R7" s="122"/>
-      <c r="S7" s="122"/>
-      <c r="T7" s="122"/>
-      <c r="U7" s="122"/>
-      <c r="V7" s="122"/>
-      <c r="W7" s="123"/>
-      <c r="X7" s="118" t="s">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="104"/>
+      <c r="Q7" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="103"/>
+      <c r="W7" s="104"/>
+      <c r="X7" s="122" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="128" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="129"/>
+      <c r="B8" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="115"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9"/>
@@ -2564,28 +2522,28 @@
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
       <c r="O8" s="10"/>
-      <c r="P8" s="126" t="s">
+      <c r="P8" s="127" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="128" t="s">
-        <v>0</v>
-      </c>
-      <c r="R8" s="133"/>
+      <c r="Q8" s="105" t="s">
+        <v>0</v>
+      </c>
+      <c r="R8" s="106"/>
       <c r="S8" s="9"/>
       <c r="T8" s="9"/>
       <c r="U8" s="9"/>
       <c r="V8" s="10"/>
-      <c r="W8" s="124" t="s">
+      <c r="W8" s="125" t="s">
         <v>21</v>
       </c>
-      <c r="X8" s="119"/>
+      <c r="X8" s="123"/>
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="2:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="108"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
@@ -2598,17 +2556,17 @@
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="17"/>
-      <c r="P9" s="126"/>
-      <c r="Q9" s="107" t="s">
+      <c r="P9" s="127"/>
+      <c r="Q9" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="R9" s="141"/>
+      <c r="R9" s="107"/>
       <c r="S9" s="16"/>
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
       <c r="V9" s="17"/>
-      <c r="W9" s="125"/>
-      <c r="X9" s="120"/>
+      <c r="W9" s="126"/>
+      <c r="X9" s="124"/>
       <c r="Y9" s="1"/>
       <c r="Z9" s="5"/>
       <c r="AA9" s="5"/>
@@ -2629,7 +2587,7 @@
       <c r="AP9" s="15"/>
     </row>
     <row r="10" spans="2:42" ht="17.100000000000001" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="131" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="63"/>
@@ -2649,11 +2607,11 @@
         <f>SUM(D10:O10)</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="98" t="s">
+      <c r="Q10" s="131" t="s">
         <v>27</v>
       </c>
       <c r="R10" s="81" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S10" s="37"/>
       <c r="T10" s="37"/>
@@ -2669,7 +2627,7 @@
       </c>
     </row>
     <row r="11" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="99"/>
+      <c r="B11" s="132"/>
       <c r="C11" s="22"/>
       <c r="D11" s="26"/>
       <c r="E11" s="26"/>
@@ -2687,9 +2645,9 @@
         <f t="shared" ref="P11:P34" si="0">SUM(D11:O11)</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="99"/>
+      <c r="Q11" s="132"/>
       <c r="R11" s="82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S11" s="26"/>
       <c r="T11" s="26"/>
@@ -2705,7 +2663,7 @@
       </c>
     </row>
     <row r="12" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="99"/>
+      <c r="B12" s="132"/>
       <c r="C12" s="22"/>
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
@@ -2723,9 +2681,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="99"/>
+      <c r="Q12" s="132"/>
       <c r="R12" s="82" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="S12" s="26"/>
       <c r="T12" s="26"/>
@@ -2741,11 +2699,11 @@
       </c>
     </row>
     <row r="13" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="100" t="s">
-        <v>46</v>
+      <c r="B13" s="136" t="s">
+        <v>44</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
@@ -2760,11 +2718,11 @@
       <c r="N13" s="19"/>
       <c r="O13" s="20"/>
       <c r="P13" s="44"/>
-      <c r="Q13" s="100" t="s">
-        <v>46</v>
+      <c r="Q13" s="136" t="s">
+        <v>44</v>
       </c>
       <c r="R13" s="92" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S13" s="19"/>
       <c r="T13" s="19"/>
@@ -2776,9 +2734,9 @@
       </c>
     </row>
     <row r="14" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="101"/>
+      <c r="B14" s="137"/>
       <c r="C14" s="22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26"/>
@@ -2793,9 +2751,9 @@
       <c r="N14" s="26"/>
       <c r="O14" s="27"/>
       <c r="P14" s="29"/>
-      <c r="Q14" s="101"/>
+      <c r="Q14" s="137"/>
       <c r="R14" s="82" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S14" s="26"/>
       <c r="T14" s="26"/>
@@ -2807,9 +2765,9 @@
       </c>
     </row>
     <row r="15" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="101"/>
+      <c r="B15" s="137"/>
       <c r="C15" s="22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26"/>
@@ -2824,9 +2782,9 @@
       <c r="N15" s="26"/>
       <c r="O15" s="27"/>
       <c r="P15" s="29"/>
-      <c r="Q15" s="101"/>
+      <c r="Q15" s="137"/>
       <c r="R15" s="82" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S15" s="26"/>
       <c r="T15" s="26"/>
@@ -2838,7 +2796,7 @@
       </c>
     </row>
     <row r="16" spans="2:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="102"/>
+      <c r="B16" s="138"/>
       <c r="C16" s="40"/>
       <c r="D16" s="41"/>
       <c r="E16" s="41"/>
@@ -2853,9 +2811,9 @@
       <c r="N16" s="41"/>
       <c r="O16" s="42"/>
       <c r="P16" s="43"/>
-      <c r="Q16" s="102"/>
+      <c r="Q16" s="138"/>
       <c r="R16" s="83" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="S16" s="41"/>
       <c r="T16" s="41"/>
@@ -2867,10 +2825,10 @@
       </c>
     </row>
     <row r="17" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="104"/>
+      <c r="B17" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="96"/>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
       <c r="F17" s="19"/>
@@ -2887,10 +2845,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q17" s="137" t="s">
-        <v>47</v>
-      </c>
-      <c r="R17" s="138"/>
+      <c r="Q17" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="R17" s="96"/>
       <c r="S17" s="19"/>
       <c r="T17" s="19"/>
       <c r="U17" s="19"/>
@@ -2905,10 +2863,10 @@
       </c>
     </row>
     <row r="18" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="105" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="106"/>
+      <c r="B18" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="98"/>
       <c r="D18" s="41"/>
       <c r="E18" s="41"/>
       <c r="F18" s="41"/>
@@ -2925,10 +2883,10 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q18" s="139" t="s">
-        <v>48</v>
-      </c>
-      <c r="R18" s="140"/>
+      <c r="Q18" s="97" t="s">
+        <v>46</v>
+      </c>
+      <c r="R18" s="98"/>
       <c r="S18" s="41"/>
       <c r="T18" s="41"/>
       <c r="U18" s="41"/>
@@ -2943,10 +2901,10 @@
       </c>
     </row>
     <row r="19" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="107" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="108"/>
+      <c r="B19" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="100"/>
       <c r="D19" s="87">
         <f>SUM(D10:D16)</f>
         <v>0</v>
@@ -2999,10 +2957,10 @@
         <f>SUM(D19:O19)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="107" t="s">
-        <v>49</v>
-      </c>
-      <c r="R19" s="108"/>
+      <c r="Q19" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="R19" s="100"/>
       <c r="S19" s="3">
         <f>SUM(S10:S16)</f>
         <v>0</v>
@@ -3029,11 +2987,11 @@
       </c>
     </row>
     <row r="20" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="142" t="s">
-        <v>45</v>
+      <c r="B20" s="139" t="s">
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -3052,31 +3010,31 @@
       </c>
       <c r="Q20" s="89"/>
       <c r="R20" s="80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S20" s="86" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="T20" s="77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U20" s="77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V20" s="78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="W20" s="79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="X20" s="76">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="143"/>
+      <c r="B21" s="140"/>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -3095,29 +3053,29 @@
       </c>
       <c r="Q21" s="90"/>
       <c r="R21" s="80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="S21" s="77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="T21" s="77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U21" s="77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="V21" s="78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="W21" s="79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="X21" s="76">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="130" t="s">
+      <c r="B22" s="109" t="s">
         <v>5</v>
       </c>
       <c r="C22" s="64" t="s">
@@ -3139,7 +3097,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="130" t="s">
+      <c r="Q22" s="109" t="s">
         <v>5</v>
       </c>
       <c r="R22" s="84" t="s">
@@ -3159,7 +3117,7 @@
       </c>
     </row>
     <row r="23" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="101"/>
+      <c r="B23" s="94"/>
       <c r="C23" s="22" t="s">
         <v>12</v>
       </c>
@@ -3179,7 +3137,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q23" s="101"/>
+      <c r="Q23" s="94"/>
       <c r="R23" s="82" t="s">
         <v>12</v>
       </c>
@@ -3197,7 +3155,7 @@
       </c>
     </row>
     <row r="24" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="101"/>
+      <c r="B24" s="94"/>
       <c r="C24" s="22" t="s">
         <v>8</v>
       </c>
@@ -3217,7 +3175,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q24" s="101"/>
+      <c r="Q24" s="94"/>
       <c r="R24" s="82" t="s">
         <v>8</v>
       </c>
@@ -3235,7 +3193,7 @@
       </c>
     </row>
     <row r="25" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="101"/>
+      <c r="B25" s="94"/>
       <c r="C25" s="22" t="s">
         <v>29</v>
       </c>
@@ -3255,7 +3213,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q25" s="101"/>
+      <c r="Q25" s="94"/>
       <c r="R25" s="82" t="s">
         <v>29</v>
       </c>
@@ -3273,7 +3231,7 @@
       </c>
     </row>
     <row r="26" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="101"/>
+      <c r="B26" s="94"/>
       <c r="C26" s="22" t="s">
         <v>9</v>
       </c>
@@ -3293,7 +3251,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q26" s="101"/>
+      <c r="Q26" s="94"/>
       <c r="R26" s="82" t="s">
         <v>9</v>
       </c>
@@ -3311,7 +3269,7 @@
       </c>
     </row>
     <row r="27" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="101"/>
+      <c r="B27" s="94"/>
       <c r="C27" s="61"/>
       <c r="D27" s="30"/>
       <c r="E27" s="30"/>
@@ -3329,7 +3287,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q27" s="101"/>
+      <c r="Q27" s="94"/>
       <c r="R27" s="85"/>
       <c r="S27" s="30"/>
       <c r="T27" s="30"/>
@@ -3345,7 +3303,7 @@
       </c>
     </row>
     <row r="28" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="101"/>
+      <c r="B28" s="94"/>
       <c r="C28" s="2" t="s">
         <v>30</v>
       </c>
@@ -3401,7 +3359,7 @@
         <f>SUM(D28:O28)</f>
         <v>0</v>
       </c>
-      <c r="Q28" s="101"/>
+      <c r="Q28" s="94"/>
       <c r="R28" s="80" t="s">
         <v>30</v>
       </c>
@@ -3431,7 +3389,7 @@
       </c>
     </row>
     <row r="29" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="101"/>
+      <c r="B29" s="94"/>
       <c r="C29" s="64"/>
       <c r="D29" s="65"/>
       <c r="E29" s="65"/>
@@ -3449,7 +3407,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q29" s="101"/>
+      <c r="Q29" s="94"/>
       <c r="R29" s="84"/>
       <c r="S29" s="65"/>
       <c r="T29" s="65"/>
@@ -3465,9 +3423,9 @@
       </c>
     </row>
     <row r="30" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="101"/>
+      <c r="B30" s="94"/>
       <c r="C30" s="22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D30" s="26"/>
       <c r="E30" s="26"/>
@@ -3485,9 +3443,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q30" s="101"/>
+      <c r="Q30" s="94"/>
       <c r="R30" s="82" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="S30" s="26"/>
       <c r="T30" s="26"/>
@@ -3503,9 +3461,9 @@
       </c>
     </row>
     <row r="31" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="101"/>
+      <c r="B31" s="94"/>
       <c r="C31" s="22" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D31" s="26"/>
       <c r="E31" s="26"/>
@@ -3523,9 +3481,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q31" s="101"/>
+      <c r="Q31" s="94"/>
       <c r="R31" s="82" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="S31" s="26"/>
       <c r="T31" s="26"/>
@@ -3541,10 +3499,8 @@
       </c>
     </row>
     <row r="32" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="101"/>
-      <c r="C32" s="22" t="s">
-        <v>32</v>
-      </c>
+      <c r="B32" s="94"/>
+      <c r="C32" s="22"/>
       <c r="D32" s="26"/>
       <c r="E32" s="26"/>
       <c r="F32" s="26"/>
@@ -3561,7 +3517,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q32" s="101"/>
+      <c r="Q32" s="94"/>
       <c r="R32" s="82"/>
       <c r="S32" s="26"/>
       <c r="T32" s="26"/>
@@ -3577,10 +3533,8 @@
       </c>
     </row>
     <row r="33" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="101"/>
-      <c r="C33" s="22" t="s">
-        <v>31</v>
-      </c>
+      <c r="B33" s="94"/>
+      <c r="C33" s="22"/>
       <c r="D33" s="26"/>
       <c r="E33" s="26"/>
       <c r="F33" s="26"/>
@@ -3597,7 +3551,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q33" s="101"/>
+      <c r="Q33" s="94"/>
       <c r="R33" s="82"/>
       <c r="S33" s="26"/>
       <c r="T33" s="26"/>
@@ -3613,7 +3567,7 @@
       </c>
     </row>
     <row r="34" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="131"/>
+      <c r="B34" s="110"/>
       <c r="C34" s="40"/>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
@@ -3631,7 +3585,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q34" s="131"/>
+      <c r="Q34" s="110"/>
       <c r="R34" s="83"/>
       <c r="S34" s="41"/>
       <c r="T34" s="41"/>
@@ -3647,10 +3601,10 @@
       </c>
     </row>
     <row r="35" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="132" t="s">
+      <c r="B35" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="129"/>
+      <c r="C35" s="115"/>
       <c r="D35" s="4">
         <f>SUM(D30:D33)+D28</f>
         <v>0</v>
@@ -3703,10 +3657,10 @@
         <f>SUM(D35:O35)</f>
         <v>0</v>
       </c>
-      <c r="Q35" s="132" t="s">
+      <c r="Q35" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="R35" s="133"/>
+      <c r="R35" s="106"/>
       <c r="S35" s="3">
         <f>SUM(S30:S31)+S28</f>
         <v>0</v>
@@ -3733,10 +3687,10 @@
       </c>
     </row>
     <row r="36" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="134" t="s">
+      <c r="B36" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="136"/>
+      <c r="C36" s="114"/>
       <c r="D36" s="7">
         <f>D19-D35</f>
         <v>0</v>
@@ -3789,10 +3743,10 @@
         <f>SUM(D36:O36)</f>
         <v>0</v>
       </c>
-      <c r="Q36" s="134" t="s">
+      <c r="Q36" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="R36" s="135"/>
+      <c r="R36" s="113"/>
       <c r="S36" s="7">
         <f>S19-S35</f>
         <v>0</v>
@@ -3820,7 +3774,7 @@
     </row>
     <row r="37" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
     <row r="38" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="109" t="s">
+      <c r="B38" s="133" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="49" t="s">
@@ -3839,10 +3793,10 @@
       <c r="N38" s="50"/>
       <c r="O38" s="51"/>
       <c r="P38" s="52"/>
-      <c r="Q38" s="94" t="s">
-        <v>35</v>
-      </c>
-      <c r="R38" s="95"/>
+      <c r="Q38" s="128" t="s">
+        <v>33</v>
+      </c>
+      <c r="R38" s="129"/>
       <c r="S38" s="73"/>
       <c r="T38" s="53"/>
       <c r="U38" s="53"/>
@@ -3851,9 +3805,9 @@
       <c r="X38" s="8"/>
     </row>
     <row r="39" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="110"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="64" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D39" s="70"/>
       <c r="E39" s="70"/>
@@ -3878,9 +3832,9 @@
       <c r="X39" s="48"/>
     </row>
     <row r="40" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="110"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="64" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D40" s="70"/>
       <c r="E40" s="70"/>
@@ -3905,9 +3859,9 @@
       <c r="X40" s="48"/>
     </row>
     <row r="41" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="110"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="64" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D41" s="70"/>
       <c r="E41" s="70"/>
@@ -3932,7 +3886,7 @@
       <c r="X41" s="48"/>
     </row>
     <row r="42" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="110"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="22" t="s">
         <v>2</v>
       </c>
@@ -3959,7 +3913,7 @@
       <c r="X42" s="48"/>
     </row>
     <row r="43" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="110"/>
+      <c r="B43" s="134"/>
       <c r="C43" s="22" t="s">
         <v>3</v>
       </c>
@@ -3986,7 +3940,7 @@
       <c r="X43" s="48"/>
     </row>
     <row r="44" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="110"/>
+      <c r="B44" s="134"/>
       <c r="C44" s="22" t="s">
         <v>4</v>
       </c>
@@ -4013,9 +3967,9 @@
       <c r="X44" s="48"/>
     </row>
     <row r="45" spans="2:24" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="110"/>
+      <c r="B45" s="134"/>
       <c r="C45" s="61" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D45" s="30"/>
       <c r="E45" s="30"/>
@@ -4040,9 +3994,9 @@
       <c r="X45" s="48"/>
     </row>
     <row r="46" spans="2:24" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="111"/>
+      <c r="B46" s="135"/>
       <c r="C46" s="91" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -4068,35 +4022,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="Q13:Q16"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="U4:V4"/>
-    <mergeCell ref="Q7:W7"/>
-    <mergeCell ref="Q8:R8"/>
-    <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="W4:X4"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Q22:Q34"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B22:B34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B2:X2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="B7:P7"/>
-    <mergeCell ref="W8:W9"/>
-    <mergeCell ref="P8:P9"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="B8:C8"/>
     <mergeCell ref="Q38:R38"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="R4:S4"/>
@@ -4113,6 +4038,35 @@
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="Q10:Q12"/>
     <mergeCell ref="B38:B46"/>
+    <mergeCell ref="B2:X2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="B7:P7"/>
+    <mergeCell ref="W8:W9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="Q22:Q34"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B22:B34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="Q13:Q16"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="U4:V4"/>
+    <mergeCell ref="Q7:W7"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="W5:X5"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.27559055118110237" right="0.11811023622047245" top="0.27559055118110237" bottom="0.19685039370078741" header="0" footer="0"/>
